--- a/exemplos/quantitativo-exemplo-aiarq.xlsx
+++ b/exemplos/quantitativo-exemplo-aiarq.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Comparativo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orçamento" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referências SINAPI-TCPO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referências SINAPI" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3647,21 +3647,21 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>REFERÊNCIAS SINAPI / TCPO BIM — códigos oficiais por item</t>
+          <t>REFERÊNCIAS SINAPI — códigos oficiais por item</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>SINAPI (Caixa) = referência oficial de preço/quantitativo no Brasil — atualizado mensalmente. TCPO BIM (Pini) = composição técnica com insumos detalhados. Cada item do quantitativo recebe os matches mais próximos pra você buscar preço/composição.</t>
+          <t>SINAPI (Caixa) = referência oficial de preço/quantitativo no Brasil, atualizada mensalmente. Cada item do quantitativo recebe os códigos SINAPI mais próximos pra você buscar o preço/composição.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>AI.arq NÃO entrega preço. Use o código pra consultar o preço atualizado no SINAPI oficial (https://www.caixa.gov.br) ou TCPO BIM. Matches marcados com ~ usaram busca simplificada — confirmar adequação.</t>
+          <t>AI.arq NÃO entrega preço. Use o código pra consultar o preço atualizado no SINAPI oficial (https://www.caixa.gov.br). Matches marcados com ~ usaram busca simplificada — confirmar adequação.</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="E85" s="68" t="inlineStr">
         <is>
-          <t>Sem match SINAPI nem TCPO (descrição muito específica) — buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+          <t>Sem match SINAPI (descrição muito específica) — buscar manualmente em https://www.caixa.gov.br/sinapi</t>
         </is>
       </c>
       <c r="F85" s="69" t="n"/>
@@ -5773,7 +5773,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Como ler: MATCH % indica a similaridade entre a descrição do item e a composição SINAPI/TCPO. Acima de 70% = referência forte. 40-70% = revisar. Abaixo de 30% = candidato fraco, buscar código manualmente em https://www.caixa.gov.br/sinapi.</t>
+          <t>Como ler: MATCH % indica a similaridade entre a descrição do item e a composição SINAPI. Acima de 70% = referência forte. 40-70% = revisar. Abaixo de 30% = candidato fraco, buscar código manualmente em https://www.caixa.gov.br/sinapi.</t>
         </is>
       </c>
     </row>

--- a/exemplos/quantitativo-exemplo-aiarq.xlsx
+++ b/exemplos/quantitativo-exemplo-aiarq.xlsx
@@ -221,12 +221,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -402,6 +402,18 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -411,35 +423,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 90776 (conf. alta) · Legenda/estimativa</t>
+          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~99815 (conf. alta) ⚠ unidade difere (item m² × SINAPI UN) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 97624 (conf. alta) ⚠ unidade difere (item m² × SINAPI M3) · Legenda/estimativa</t>
+          <t>SINAPI 97622 (conf. alta) ⚠ unidade difere (item m² × SINAPI M3)</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~97635 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
-          <t>SINAPI: sem correspondência forte (ver aba técnica) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI ~96114 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I20" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~99054 (conf. alta) ⚠ unidade difere (item m × SINAPI M2) · Legenda/estimativa</t>
+          <t>SINAPI 99054 (conf. alta) ⚠ unidade difere (item m × SINAPI M2)</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="I23" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 105542 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 105542 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I24" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 106773 (conf. média) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI ~105546 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="I25" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~95696 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I28" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~92010 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI ~92004 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I29" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 91955 (conf. média) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI ~91953 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I30" s="22" t="inlineStr">
         <is>
-          <t>Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 106077 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="I33" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 86888 (conf. alta) · Legenda/estimativa</t>
+          <t>SINAPI 86888 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~106773 (conf. alta) · Legenda/estimativa</t>
+          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 103272 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 103271 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 89306 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 89290 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~102238 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 96361 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~88478 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI ~88478 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~98671 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 87261 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I46" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~88650 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI ~88650 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I47" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~106790 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 101728 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="I50" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 95626 (conf. média) · Legenda/estimativa</t>
+          <t>SINAPI ~88489 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="I51" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~102232 (conf. alta) · Legenda/estimativa</t>
+          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I54" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~105472 (conf. alta) ⚠ unidade difere (item un × SINAPI T) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 91297 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="I55" s="22" t="inlineStr">
         <is>
-          <t>SINAPI 102182 (conf. alta) · Prancha ARQ-EXEC-01</t>
+          <t>SINAPI 102184 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3661,7 +3661,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>AI.arq NÃO entrega preço. Use o código pra consultar o preço atualizado no SINAPI oficial (https://www.caixa.gov.br). Matches marcados com ~ usaram busca simplificada — confirmar adequação.</t>
+          <t>AI.arq NÃO entrega preço. Use o código pra consultar o preço atualizado no SINAPI oficial (https://www.caixa.gov.br). A busca por texto levanta os candidatos e a IA escolhe qual é o mesmo serviço: "✓ IA conferiu" é o escolhido (vai pra coluna REF do orçamento); os demais são alternativas com o % de semelhança do TEXTO, que erra — confira sempre a composição oficial ao lado antes de usar.</t>
         </is>
       </c>
     </row>
@@ -3718,2060 +3718,1905 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>Administração da obra e mobilização de canteiro</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="58" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+        </is>
+      </c>
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="60" t="n"/>
+      <c r="H6" s="60" t="n"/>
+      <c r="I6" s="60" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Limpeza final da obra</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="E7" s="59" t="inlineStr">
+        <is>
+          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+        </is>
+      </c>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="60" t="n"/>
+      <c r="H7" s="60" t="n"/>
+      <c r="I7" s="60" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="61" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Demolição de alvenaria de vedação (e=15cm)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E8" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F6" s="59" t="n"/>
-      <c r="G6" s="59" t="n"/>
-      <c r="H6" s="59" t="n"/>
-      <c r="I6" s="59" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="60" t="inlineStr"/>
-      <c r="B7" s="61" t="inlineStr"/>
-      <c r="C7" s="62" t="n"/>
-      <c r="D7" s="62" t="n"/>
-      <c r="E7" s="63" t="inlineStr">
+      <c r="F8" s="63" t="n"/>
+      <c r="G8" s="63" t="n"/>
+      <c r="H8" s="63" t="n"/>
+      <c r="I8" s="63" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="64" t="inlineStr"/>
+      <c r="B9" s="65" t="inlineStr"/>
+      <c r="C9" s="66" t="n"/>
+      <c r="D9" s="66" t="n"/>
+      <c r="E9" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr">
-        <is>
-          <t>90776</t>
-        </is>
-      </c>
-      <c r="G7" s="64" t="inlineStr">
-        <is>
-          <t>ENCARREGADO GERAL COM ENCARGOS COMPLEMENTARES</t>
-        </is>
-      </c>
-      <c r="H7" s="65" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I7" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="60" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr"/>
-      <c r="C8" s="62" t="n"/>
-      <c r="D8" s="62" t="n"/>
-      <c r="E8" s="63" t="inlineStr">
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>97622</t>
+        </is>
+      </c>
+      <c r="G9" s="68" t="inlineStr">
+        <is>
+          <t>DEMOLIÇÃO DE ALVENARIA DE BLOCO FURADO, DE FORMA MANUAL, SEM REAPROVEITAMENTO. AF_09/2023</t>
+        </is>
+      </c>
+      <c r="H9" s="69" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="I9" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="64" t="inlineStr"/>
+      <c r="B10" s="65" t="inlineStr"/>
+      <c r="C10" s="66" t="n"/>
+      <c r="D10" s="66" t="n"/>
+      <c r="E10" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F8" s="63" t="inlineStr">
-        <is>
-          <t>93572</t>
-        </is>
-      </c>
-      <c r="G8" s="64" t="inlineStr">
-        <is>
-          <t>ENCARREGADO GERAL DE OBRAS COM ENCARGOS COMPLEMENTARES</t>
-        </is>
-      </c>
-      <c r="H8" s="65" t="inlineStr">
-        <is>
-          <t>MES</t>
-        </is>
-      </c>
-      <c r="I8" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="57" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>Limpeza final da obra</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>~97632</t>
+        </is>
+      </c>
+      <c r="G10" s="68" t="inlineStr">
+        <is>
+          <t>DEMOLIÇÃO DE RODAPÉ CERÂMICO, DE FORMA MANUAL, SEM REAPROVEITAMENTO. AF_09/2023</t>
+        </is>
+      </c>
+      <c r="H10" s="69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I10" s="67" t="inlineStr">
+        <is>
+          <t>32% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>Remoção de divisória existente</t>
+        </is>
+      </c>
+      <c r="C12" s="57" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E10" s="58" t="inlineStr">
+      <c r="D12" s="57" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="59" t="inlineStr">
+        <is>
+          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+        </is>
+      </c>
+      <c r="F12" s="60" t="n"/>
+      <c r="G12" s="60" t="n"/>
+      <c r="H12" s="60" t="n"/>
+      <c r="I12" s="60" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Forro de gesso acartonado liso</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F10" s="59" t="n"/>
-      <c r="G10" s="59" t="n"/>
-      <c r="H10" s="59" t="n"/>
-      <c r="I10" s="59" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="60" t="inlineStr"/>
-      <c r="B11" s="61" t="inlineStr"/>
-      <c r="C11" s="62" t="n"/>
-      <c r="D11" s="62" t="n"/>
-      <c r="E11" s="63" t="inlineStr">
+      <c r="F13" s="63" t="n"/>
+      <c r="G13" s="63" t="n"/>
+      <c r="H13" s="63" t="n"/>
+      <c r="I13" s="63" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="64" t="inlineStr"/>
+      <c r="B14" s="65" t="inlineStr"/>
+      <c r="C14" s="66" t="n"/>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F11" s="63" t="inlineStr">
-        <is>
-          <t>~99815</t>
-        </is>
-      </c>
-      <c r="G11" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LIMPEZA DE BANCADA DE PIA COM PLACA DE ROCHA E CUBA DE INOX, INCLUSIVE METAIS CORRESPONDENTES. </t>
-        </is>
-      </c>
-      <c r="H11" s="65" t="inlineStr">
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>~96114</t>
+        </is>
+      </c>
+      <c r="G14" s="68" t="inlineStr">
+        <is>
+          <t>FORRO EM DRYWALL, PARA AMBIENTES COMERCIAIS, INCLUSIVE ESTRUTURA BIRECIONAL DE FIXAÇÃO. AF_08/2</t>
+        </is>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I14" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="64" t="inlineStr"/>
+      <c r="B15" s="65" t="inlineStr"/>
+      <c r="C15" s="66" t="n"/>
+      <c r="D15" s="66" t="n"/>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>~96113</t>
+        </is>
+      </c>
+      <c r="G15" s="68" t="inlineStr">
+        <is>
+          <t>FORRO EM PLACAS DE GESSO, PARA AMBIENTES COMERCIAIS. AF_08/2023_PS</t>
+        </is>
+      </c>
+      <c r="H15" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I15" s="67" t="inlineStr">
+        <is>
+          <t>41% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="61" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Sanca de gesso perimetral</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F17" s="63" t="n"/>
+      <c r="G17" s="63" t="n"/>
+      <c r="H17" s="63" t="n"/>
+      <c r="I17" s="63" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="64" t="inlineStr"/>
+      <c r="B18" s="65" t="inlineStr"/>
+      <c r="C18" s="66" t="n"/>
+      <c r="D18" s="66" t="n"/>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>99054</t>
+        </is>
+      </c>
+      <c r="G18" s="68" t="inlineStr">
+        <is>
+          <t>ACABAMENTOS PARA FORRO (SANCA DE GESSO, MONTADA NA OBRA). AF_08/2023_PS</t>
+        </is>
+      </c>
+      <c r="H18" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I18" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="64" t="inlineStr"/>
+      <c r="B19" s="65" t="inlineStr"/>
+      <c r="C19" s="66" t="n"/>
+      <c r="D19" s="66" t="n"/>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>~86904</t>
+        </is>
+      </c>
+      <c r="G19" s="68" t="inlineStr">
+        <is>
+          <t>LAVATÓRIO LOUÇA BRANCA SUSPENSO, *40 X 30* CM OU EQUIVALENTE, PADRÃO POPULAR - FORNECIMENTO E I</t>
+        </is>
+      </c>
+      <c r="H19" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I11" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="60" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr"/>
-      <c r="C12" s="62" t="n"/>
-      <c r="D12" s="62" t="n"/>
-      <c r="E12" s="63" t="inlineStr">
+      <c r="I19" s="67" t="inlineStr">
+        <is>
+          <t>15% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="61" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Luminária LED de embutir 60x60</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="n"/>
+      <c r="G21" s="63" t="n"/>
+      <c r="H21" s="63" t="n"/>
+      <c r="I21" s="63" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="64" t="inlineStr"/>
+      <c r="B22" s="65" t="inlineStr"/>
+      <c r="C22" s="66" t="n"/>
+      <c r="D22" s="66" t="n"/>
+      <c r="E22" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F12" s="63" t="inlineStr">
-        <is>
-          <t>~99818</t>
-        </is>
-      </c>
-      <c r="G12" s="64" t="inlineStr">
-        <is>
-          <t>LIMPEZA DE BACIA SANITÁRIA, BIDÊ OU MICTÓRIO EM LOUÇA, INCLUSIVE METAIS CORRESPONDENTES. AF_10/</t>
-        </is>
-      </c>
-      <c r="H12" s="65" t="inlineStr">
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>105542</t>
+        </is>
+      </c>
+      <c r="G22" s="68" t="inlineStr">
+        <is>
+          <t>LUMINÁRIA LED DE EMBUTIR - QUADRADA 60X60CM, INCLUSO DRIVER - FORNECIMENTO E INSTALAÇÃO. AF_09/</t>
+        </is>
+      </c>
+      <c r="H22" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I12" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="57" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
-        <is>
-          <t>Demolição de alvenaria de vedação (e=15cm)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E14" s="58" t="inlineStr">
+      <c r="I22" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="64" t="inlineStr"/>
+      <c r="B23" s="65" t="inlineStr"/>
+      <c r="C23" s="66" t="n"/>
+      <c r="D23" s="66" t="n"/>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>~103786</t>
+        </is>
+      </c>
+      <c r="G23" s="68" t="inlineStr">
+        <is>
+          <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 12 W - FORNECIMENTO E INSTALAÇÃO. AF_09/</t>
+        </is>
+      </c>
+      <c r="H23" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I23" s="67" t="inlineStr">
+        <is>
+          <t>44% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="61" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Spot LED de embutir redondo</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F14" s="59" t="n"/>
-      <c r="G14" s="59" t="n"/>
-      <c r="H14" s="59" t="n"/>
-      <c r="I14" s="59" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="60" t="inlineStr"/>
-      <c r="B15" s="61" t="inlineStr"/>
-      <c r="C15" s="62" t="n"/>
-      <c r="D15" s="62" t="n"/>
-      <c r="E15" s="63" t="inlineStr">
+      <c r="F25" s="63" t="n"/>
+      <c r="G25" s="63" t="n"/>
+      <c r="H25" s="63" t="n"/>
+      <c r="I25" s="63" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="64" t="inlineStr"/>
+      <c r="B26" s="65" t="inlineStr"/>
+      <c r="C26" s="66" t="n"/>
+      <c r="D26" s="66" t="n"/>
+      <c r="E26" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F15" s="63" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="G15" s="64" t="inlineStr">
-        <is>
-          <t>DEMOLIÇÃO DE ALVENARIA DE TIJOLO MACIÇO, DE FORMA MANUAL, SEM REAPROVEITAMENTO. AF_09/2023</t>
-        </is>
-      </c>
-      <c r="H15" s="65" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I15" s="63" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="60" t="inlineStr"/>
-      <c r="B16" s="61" t="inlineStr"/>
-      <c r="C16" s="62" t="n"/>
-      <c r="D16" s="62" t="n"/>
-      <c r="E16" s="63" t="inlineStr">
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>~105546</t>
+        </is>
+      </c>
+      <c r="G26" s="68" t="inlineStr">
+        <is>
+          <t>LUMINÁRIA TIPO SPOT, DE EMBUTIR, COM 1 LÂMPADA LED PAR20 - FORNECIMENTO E INSTALAÇÃO. AF_09/202</t>
+        </is>
+      </c>
+      <c r="H26" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I26" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="64" t="inlineStr"/>
+      <c r="B27" s="65" t="inlineStr"/>
+      <c r="C27" s="66" t="n"/>
+      <c r="D27" s="66" t="n"/>
+      <c r="E27" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F16" s="63" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="G16" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DEMOLIÇÃO DE ALVENARIA PARA QUALQUER TIPO DE BLOCO, DE FORMA MECANIZADA, SEM REAPROVEITAMENTO. </t>
-        </is>
-      </c>
-      <c r="H16" s="65" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I16" s="63" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="57" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>Remoção de divisória existente</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="E18" s="58" t="inlineStr">
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>~105545</t>
+        </is>
+      </c>
+      <c r="G27" s="68" t="inlineStr">
+        <is>
+          <t>LUMINÁRIA TIPO SPOT, DE SOBREPOR, COM 1 LÂMPADA LED PAR20 - FORNECIMENTO E INSTALAÇÃO. AF_09/20</t>
+        </is>
+      </c>
+      <c r="H27" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I27" s="67" t="inlineStr">
+        <is>
+          <t>28% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B29" s="58" t="inlineStr">
+        <is>
+          <t>Pendente decorativo sobre bancada</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D29" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="59" t="inlineStr">
+        <is>
+          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+        </is>
+      </c>
+      <c r="F29" s="60" t="n"/>
+      <c r="G29" s="60" t="n"/>
+      <c r="H29" s="60" t="n"/>
+      <c r="I29" s="60" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Ponto de tomada 2P+T 10A</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E30" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F18" s="59" t="n"/>
-      <c r="G18" s="59" t="n"/>
-      <c r="H18" s="59" t="n"/>
-      <c r="I18" s="59" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="60" t="inlineStr"/>
-      <c r="B19" s="61" t="inlineStr"/>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="62" t="n"/>
-      <c r="E19" s="63" t="inlineStr">
+      <c r="F30" s="63" t="n"/>
+      <c r="G30" s="63" t="n"/>
+      <c r="H30" s="63" t="n"/>
+      <c r="I30" s="63" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="64" t="inlineStr"/>
+      <c r="B31" s="65" t="inlineStr"/>
+      <c r="C31" s="66" t="n"/>
+      <c r="D31" s="66" t="n"/>
+      <c r="E31" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F19" s="63" t="inlineStr">
-        <is>
-          <t>~97635</t>
-        </is>
-      </c>
-      <c r="G19" s="64" t="inlineStr">
-        <is>
-          <t>REMOÇÃO DE PISO DE BLOCO INTERTRAVADO OU DE PEDRA PORTUGUESA, DE FORMA MANUAL, COM REAPROVEITAM</t>
-        </is>
-      </c>
-      <c r="H19" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I19" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="60" t="inlineStr"/>
-      <c r="B20" s="61" t="inlineStr"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="63" t="inlineStr">
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>~92004</t>
+        </is>
+      </c>
+      <c r="G31" s="68" t="inlineStr">
+        <is>
+          <t>TOMADA MÉDIA DE EMBUTIR (2 MÓDULOS), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INST</t>
+        </is>
+      </c>
+      <c r="H31" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I31" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="64" t="inlineStr"/>
+      <c r="B32" s="65" t="inlineStr"/>
+      <c r="C32" s="66" t="n"/>
+      <c r="D32" s="66" t="n"/>
+      <c r="E32" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F20" s="63" t="inlineStr">
-        <is>
-          <t>~104803</t>
-        </is>
-      </c>
-      <c r="G20" s="64" t="inlineStr">
-        <is>
-          <t>REMOÇÃO CALHAS E RUFOS, DE FORMA MANUAL, SEM REAPROVEITAMENTO. AF_09/2023</t>
-        </is>
-      </c>
-      <c r="H20" s="65" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I20" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="57" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>Alvenaria de bloco cerâmico e=14cm</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="E22" s="58" t="inlineStr">
+      <c r="F32" s="67" t="inlineStr">
+        <is>
+          <t>~91997</t>
+        </is>
+      </c>
+      <c r="G32" s="68" t="inlineStr">
+        <is>
+          <t>TOMADA MÉDIA DE EMBUTIR (1 MÓDULO), 2P+T 20 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTA</t>
+        </is>
+      </c>
+      <c r="H32" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I32" s="67" t="inlineStr">
+        <is>
+          <t>33% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="61" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>Ponto de interruptor</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E34" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F22" s="59" t="n"/>
-      <c r="G22" s="59" t="n"/>
-      <c r="H22" s="59" t="n"/>
-      <c r="I22" s="59" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="60" t="inlineStr"/>
-      <c r="B23" s="61" t="inlineStr"/>
-      <c r="C23" s="62" t="n"/>
-      <c r="D23" s="62" t="n"/>
-      <c r="E23" s="63" t="inlineStr">
+      <c r="F34" s="63" t="n"/>
+      <c r="G34" s="63" t="n"/>
+      <c r="H34" s="63" t="n"/>
+      <c r="I34" s="63" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr"/>
+      <c r="B35" s="65" t="inlineStr"/>
+      <c r="C35" s="66" t="n"/>
+      <c r="D35" s="66" t="n"/>
+      <c r="E35" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F23" s="63" t="inlineStr">
-        <is>
-          <t>89306</t>
-        </is>
-      </c>
-      <c r="G23" s="64" t="inlineStr">
-        <is>
-          <t>ALVENARIA ESTRUTURAL DE BLOCOS CERÂMICOS 14X19X29, (ESPESSURA DE 14 CM), UTILIZANDO COLHER DE P</t>
-        </is>
-      </c>
-      <c r="H23" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I23" s="63" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="60" t="inlineStr"/>
-      <c r="B24" s="61" t="inlineStr"/>
-      <c r="C24" s="62" t="n"/>
-      <c r="D24" s="62" t="n"/>
-      <c r="E24" s="63" t="inlineStr">
+      <c r="F35" s="67" t="inlineStr">
+        <is>
+          <t>~91953</t>
+        </is>
+      </c>
+      <c r="G35" s="68" t="inlineStr">
+        <is>
+          <t>INTERRUPTOR SIMPLES (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO</t>
+        </is>
+      </c>
+      <c r="H35" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I35" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr"/>
+      <c r="B36" s="65" t="inlineStr"/>
+      <c r="C36" s="66" t="n"/>
+      <c r="D36" s="66" t="n"/>
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F24" s="63" t="inlineStr">
-        <is>
-          <t>89307</t>
-        </is>
-      </c>
-      <c r="G24" s="64" t="inlineStr">
-        <is>
-          <t>ALVENARIA ESTRUTURAL DE BLOCOS CERÂMICOS 14X19X29, (ESPESSURA DE 14 CM), UTILIZANDO COLHER DE P</t>
-        </is>
-      </c>
-      <c r="H24" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I24" s="63" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="57" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>Divisória em drywall (2 faces, com lã)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E26" s="58" t="inlineStr">
+      <c r="F36" s="67" t="inlineStr">
+        <is>
+          <t>~91954</t>
+        </is>
+      </c>
+      <c r="G36" s="68" t="inlineStr">
+        <is>
+          <t>INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇÃO.</t>
+        </is>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I36" s="67" t="inlineStr">
+        <is>
+          <t>61% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="61" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Ponto de rede/dados RJ45 cat6</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F26" s="59" t="n"/>
-      <c r="G26" s="59" t="n"/>
-      <c r="H26" s="59" t="n"/>
-      <c r="I26" s="59" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="60" t="inlineStr"/>
-      <c r="B27" s="61" t="inlineStr"/>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="62" t="n"/>
-      <c r="E27" s="63" t="inlineStr">
+      <c r="F38" s="63" t="n"/>
+      <c r="G38" s="63" t="n"/>
+      <c r="H38" s="63" t="n"/>
+      <c r="I38" s="63" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr"/>
+      <c r="B39" s="65" t="inlineStr"/>
+      <c r="C39" s="66" t="n"/>
+      <c r="D39" s="66" t="n"/>
+      <c r="E39" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F27" s="63" t="inlineStr">
-        <is>
-          <t>~102238</t>
-        </is>
-      </c>
-      <c r="G27" s="64" t="inlineStr">
-        <is>
-          <t>DIVISORIA CEGA (N1) - PAINEL MDF, LINHA 90 MM - PERFIS DE ALUMÍNIO EXTRUDADO. AF_10/2025</t>
-        </is>
-      </c>
-      <c r="H27" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I27" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="60" t="inlineStr"/>
-      <c r="B28" s="61" t="inlineStr"/>
-      <c r="C28" s="62" t="n"/>
-      <c r="D28" s="62" t="n"/>
-      <c r="E28" s="63" t="inlineStr">
+      <c r="F39" s="67" t="inlineStr">
+        <is>
+          <t>106077</t>
+        </is>
+      </c>
+      <c r="G39" s="68" t="inlineStr">
+        <is>
+          <t>TOMADA RJ45 CAT 6E (COMPLETA) - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+        </is>
+      </c>
+      <c r="H39" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I39" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr"/>
+      <c r="B40" s="65" t="inlineStr"/>
+      <c r="C40" s="66" t="n"/>
+      <c r="D40" s="66" t="n"/>
+      <c r="E40" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F28" s="63" t="inlineStr">
-        <is>
-          <t>~102253</t>
-        </is>
-      </c>
-      <c r="G28" s="64" t="inlineStr">
-        <is>
-          <t>DIVISORIA SANITÁRIA, EM GRANITO CINZA POLIDO, ESP = 3CM, ASSENTADO COM ARGAMASSA COLANTE AC III</t>
-        </is>
-      </c>
-      <c r="H28" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I28" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="57" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B30" s="43" t="inlineStr">
-        <is>
-          <t>Contrapiso desempenado e=4cm</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E30" s="58" t="inlineStr">
+      <c r="F40" s="67" t="inlineStr">
+        <is>
+          <t>98307</t>
+        </is>
+      </c>
+      <c r="G40" s="68" t="inlineStr">
+        <is>
+          <t>TOMADA DE REDE RJ45 - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+        </is>
+      </c>
+      <c r="H40" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I40" s="67" t="inlineStr">
+        <is>
+          <t>40% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="61" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>Bacia sanitária com caixa acoplada</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F30" s="59" t="n"/>
-      <c r="G30" s="59" t="n"/>
-      <c r="H30" s="59" t="n"/>
-      <c r="I30" s="59" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="60" t="inlineStr"/>
-      <c r="B31" s="61" t="inlineStr"/>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="62" t="n"/>
-      <c r="E31" s="63" t="inlineStr">
+      <c r="F42" s="63" t="n"/>
+      <c r="G42" s="63" t="n"/>
+      <c r="H42" s="63" t="n"/>
+      <c r="I42" s="63" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr"/>
+      <c r="B43" s="65" t="inlineStr"/>
+      <c r="C43" s="66" t="n"/>
+      <c r="D43" s="66" t="n"/>
+      <c r="E43" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F31" s="63" t="inlineStr">
-        <is>
-          <t>~88478</t>
-        </is>
-      </c>
-      <c r="G31" s="64" t="inlineStr">
-        <is>
-          <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 4CM. AF_07/2021</t>
-        </is>
-      </c>
-      <c r="H31" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I31" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="60" t="inlineStr"/>
-      <c r="B32" s="61" t="inlineStr"/>
-      <c r="C32" s="62" t="n"/>
-      <c r="D32" s="62" t="n"/>
-      <c r="E32" s="63" t="inlineStr">
+      <c r="F43" s="67" t="inlineStr">
+        <is>
+          <t>86888</t>
+        </is>
+      </c>
+      <c r="G43" s="68" t="inlineStr">
+        <is>
+          <t>BACIA SANITÁRIA COM CAIXA ACOPLADA LOUÇA BRANCA - FORNECIMENTO E INSTALAÇÃO. AF_02/2026</t>
+        </is>
+      </c>
+      <c r="H43" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I43" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="64" t="inlineStr"/>
+      <c r="B44" s="65" t="inlineStr"/>
+      <c r="C44" s="66" t="n"/>
+      <c r="D44" s="66" t="n"/>
+      <c r="E44" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F32" s="63" t="inlineStr">
-        <is>
-          <t>~88477</t>
-        </is>
-      </c>
-      <c r="G32" s="64" t="inlineStr">
-        <is>
-          <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 3CM. AF_07/2021</t>
-        </is>
-      </c>
-      <c r="H32" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I32" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="57" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>Piso porcelanato retificado 60x60</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="E34" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F34" s="59" t="n"/>
-      <c r="G34" s="59" t="n"/>
-      <c r="H34" s="59" t="n"/>
-      <c r="I34" s="59" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="60" t="inlineStr"/>
-      <c r="B35" s="61" t="inlineStr"/>
-      <c r="C35" s="62" t="n"/>
-      <c r="D35" s="62" t="n"/>
-      <c r="E35" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F35" s="63" t="inlineStr">
-        <is>
-          <t>~98671</t>
-        </is>
-      </c>
-      <c r="G35" s="64" t="inlineStr">
-        <is>
-          <t>PISO EM GRANITO APLICADO EM AMBIENTES INTERNOS. AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H35" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I35" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="60" t="inlineStr"/>
-      <c r="B36" s="61" t="inlineStr"/>
-      <c r="C36" s="62" t="n"/>
-      <c r="D36" s="62" t="n"/>
-      <c r="E36" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F36" s="63" t="inlineStr">
-        <is>
-          <t>~101732</t>
-        </is>
-      </c>
-      <c r="G36" s="64" t="inlineStr">
-        <is>
-          <t>PISO EM PEDRA ARDÓSIA ASSENTADO SOBRE ARGAMASSA 1:3 (CIMENTO E AREIA). AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H36" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I36" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="57" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
-        <is>
-          <t>Rodapé em porcelanato h=7cm</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="E38" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F38" s="59" t="n"/>
-      <c r="G38" s="59" t="n"/>
-      <c r="H38" s="59" t="n"/>
-      <c r="I38" s="59" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="60" t="inlineStr"/>
-      <c r="B39" s="61" t="inlineStr"/>
-      <c r="C39" s="62" t="n"/>
-      <c r="D39" s="62" t="n"/>
-      <c r="E39" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F39" s="63" t="inlineStr">
-        <is>
-          <t>~88650</t>
-        </is>
-      </c>
-      <c r="G39" s="64" t="inlineStr">
-        <is>
-          <t>RODAPÉ CERÂMICO DE 7CM DE ALTURA COM PLACAS TIPO ESMALTADA DE DIMENSÕES 60X60CM. AF_02/2023</t>
-        </is>
-      </c>
-      <c r="H39" s="65" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I39" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="60" t="inlineStr"/>
-      <c r="B40" s="61" t="inlineStr"/>
-      <c r="C40" s="62" t="n"/>
-      <c r="D40" s="62" t="n"/>
-      <c r="E40" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F40" s="63" t="inlineStr">
-        <is>
-          <t>~101739</t>
-        </is>
-      </c>
-      <c r="G40" s="64" t="inlineStr">
-        <is>
-          <t>RODAPÉ EM MADEIRA, ALTURA 7CM, FIXADO COM COLA PVA E PREGOS. AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H40" s="65" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I40" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="57" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
-        <is>
-          <t>Piso vinílico em manta (sala de reunião)</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E42" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F42" s="59" t="n"/>
-      <c r="G42" s="59" t="n"/>
-      <c r="H42" s="59" t="n"/>
-      <c r="I42" s="59" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="60" t="inlineStr"/>
-      <c r="B43" s="61" t="inlineStr"/>
-      <c r="C43" s="62" t="n"/>
-      <c r="D43" s="62" t="n"/>
-      <c r="E43" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F43" s="63" t="inlineStr">
-        <is>
-          <t>~106790</t>
-        </is>
-      </c>
-      <c r="G43" s="64" t="inlineStr">
-        <is>
-          <t>PISO VINÍLICO SEMI-FLEXÍVEL EM RÉGUAS, PADRÃO LISO, ESPESSURA 3,2 MM, FIXADO COM COLA. AF_02/20</t>
-        </is>
-      </c>
-      <c r="H43" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I43" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="60" t="inlineStr"/>
-      <c r="B44" s="61" t="inlineStr"/>
-      <c r="C44" s="62" t="n"/>
-      <c r="D44" s="62" t="n"/>
-      <c r="E44" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F44" s="63" t="inlineStr">
-        <is>
-          <t>~101728</t>
-        </is>
-      </c>
-      <c r="G44" s="64" t="inlineStr">
-        <is>
-          <t>PISO VINÍLICO FLEXÍVEL EM MANTA, PADRÃO LISO, ESPESSURA 2 MM, FIXADO COM COLA. AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H44" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I44" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="F44" s="67" t="inlineStr">
+        <is>
+          <t>~100848</t>
+        </is>
+      </c>
+      <c r="G44" s="68" t="inlineStr">
+        <is>
+          <t>BACIA SANITÁRIA INFANTIL LOUÇA BRANCA, COM TUBO DE LIGAÇÃO CROMADO - FORNECIMENTO E INSTALAÇÃO.</t>
+        </is>
+      </c>
+      <c r="H44" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I44" s="67" t="inlineStr">
+        <is>
+          <t>45% (texto)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="57" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B46" s="43" t="inlineStr">
-        <is>
-          <t>Forro de gesso acartonado liso</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="inlineStr">
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B46" s="58" t="inlineStr">
+        <is>
+          <t>Cuba de apoio + torneira (copa)</t>
+        </is>
+      </c>
+      <c r="C46" s="57" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D46" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="59" t="inlineStr">
+        <is>
+          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+        </is>
+      </c>
+      <c r="F46" s="60" t="n"/>
+      <c r="G46" s="60" t="n"/>
+      <c r="H46" s="60" t="n"/>
+      <c r="I46" s="60" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>Ar-condicionado split cassete 36.000 BTU</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F47" s="63" t="n"/>
+      <c r="G47" s="63" t="n"/>
+      <c r="H47" s="63" t="n"/>
+      <c r="I47" s="63" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="64" t="inlineStr"/>
+      <c r="B48" s="65" t="inlineStr"/>
+      <c r="C48" s="66" t="n"/>
+      <c r="D48" s="66" t="n"/>
+      <c r="E48" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F48" s="67" t="inlineStr">
+        <is>
+          <t>103271</t>
+        </is>
+      </c>
+      <c r="G48" s="68" t="inlineStr">
+        <is>
+          <t>AR CONDICIONADO SPLIT ON/OFF, CASSETE (TETO), FRIO 4 VIAS 36000 BTU/H - FORNECIMENTO E INSTALAÇ</t>
+        </is>
+      </c>
+      <c r="H48" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I48" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="64" t="inlineStr"/>
+      <c r="B49" s="65" t="inlineStr"/>
+      <c r="C49" s="66" t="n"/>
+      <c r="D49" s="66" t="n"/>
+      <c r="E49" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F49" s="67" t="inlineStr">
+        <is>
+          <t>~89866</t>
+        </is>
+      </c>
+      <c r="G49" s="68" t="inlineStr">
+        <is>
+          <t>JOELHO 90 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM DRENO DE AR-CONDICIONADO - FORNECIMENTO E</t>
+        </is>
+      </c>
+      <c r="H49" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I49" s="67" t="inlineStr">
+        <is>
+          <t>40% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="inlineStr">
+        <is>
+          <t>Alvenaria de bloco cerâmico e=14cm</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D46" s="23" t="n">
+      <c r="D51" s="23" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E51" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F51" s="63" t="n"/>
+      <c r="G51" s="63" t="n"/>
+      <c r="H51" s="63" t="n"/>
+      <c r="I51" s="63" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="64" t="inlineStr"/>
+      <c r="B52" s="65" t="inlineStr"/>
+      <c r="C52" s="66" t="n"/>
+      <c r="D52" s="66" t="n"/>
+      <c r="E52" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F52" s="67" t="inlineStr">
+        <is>
+          <t>89290</t>
+        </is>
+      </c>
+      <c r="G52" s="68" t="inlineStr">
+        <is>
+          <t>ALVENARIA ESTRUTURAL DE BLOCOS CERÂMICOS 14X19X29, (ESPESSURA DE 14 CM), UTILIZANDO PALHETA E A</t>
+        </is>
+      </c>
+      <c r="H52" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I52" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="64" t="inlineStr"/>
+      <c r="B53" s="65" t="inlineStr"/>
+      <c r="C53" s="66" t="n"/>
+      <c r="D53" s="66" t="n"/>
+      <c r="E53" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F53" s="67" t="inlineStr">
+        <is>
+          <t>~104441</t>
+        </is>
+      </c>
+      <c r="G53" s="68" t="inlineStr">
+        <is>
+          <t>ALVENARIA DE BLOCOS DE CONCRETO ESTRUTURAL 14X19X39 CM (ESPESSURA 14 CM), FBK = 8 MPA, UTILIZAN</t>
+        </is>
+      </c>
+      <c r="H53" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I53" s="67" t="inlineStr">
+        <is>
+          <t>52% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t>Divisória em drywall (2 faces, com lã)</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E55" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F55" s="63" t="n"/>
+      <c r="G55" s="63" t="n"/>
+      <c r="H55" s="63" t="n"/>
+      <c r="I55" s="63" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="64" t="inlineStr"/>
+      <c r="B56" s="65" t="inlineStr"/>
+      <c r="C56" s="66" t="n"/>
+      <c r="D56" s="66" t="n"/>
+      <c r="E56" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F56" s="67" t="inlineStr">
+        <is>
+          <t>96361</t>
+        </is>
+      </c>
+      <c r="G56" s="68" t="inlineStr">
+        <is>
+          <t>PAREDE COM SISTEMA EM CHAPAS DE GESSO PARA DRYWALL, USO INTERNO, COM DUAS FACES SIMPLES E ESTRU</t>
+        </is>
+      </c>
+      <c r="H56" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I56" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="64" t="inlineStr"/>
+      <c r="B57" s="65" t="inlineStr"/>
+      <c r="C57" s="66" t="n"/>
+      <c r="D57" s="66" t="n"/>
+      <c r="E57" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F57" s="67" t="inlineStr">
+        <is>
+          <t>~102450</t>
+        </is>
+      </c>
+      <c r="G57" s="68" t="inlineStr">
+        <is>
+          <t>DIVISORIA (N2) - PAINEL/VIDRO - PAINEL C/ MSO/COMEIA E=35MM - PERFIS SIMPLES ACO GALVANIZADO PI</t>
+        </is>
+      </c>
+      <c r="H57" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I57" s="67" t="inlineStr">
+        <is>
+          <t>28% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="61" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t>Contrapiso desempenado e=4cm</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="E59" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F59" s="63" t="n"/>
+      <c r="G59" s="63" t="n"/>
+      <c r="H59" s="63" t="n"/>
+      <c r="I59" s="63" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="64" t="inlineStr"/>
+      <c r="B60" s="65" t="inlineStr"/>
+      <c r="C60" s="66" t="n"/>
+      <c r="D60" s="66" t="n"/>
+      <c r="E60" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F60" s="67" t="inlineStr">
+        <is>
+          <t>~88478</t>
+        </is>
+      </c>
+      <c r="G60" s="68" t="inlineStr">
+        <is>
+          <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 4CM. AF_07/2021</t>
+        </is>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I60" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="64" t="inlineStr"/>
+      <c r="B61" s="65" t="inlineStr"/>
+      <c r="C61" s="66" t="n"/>
+      <c r="D61" s="66" t="n"/>
+      <c r="E61" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F61" s="67" t="inlineStr">
+        <is>
+          <t>~88476</t>
+        </is>
+      </c>
+      <c r="G61" s="68" t="inlineStr">
+        <is>
+          <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 2CM. AF_07/2021</t>
+        </is>
+      </c>
+      <c r="H61" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I61" s="67" t="inlineStr">
+        <is>
+          <t>37% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="61" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B63" s="43" t="inlineStr">
+        <is>
+          <t>Piso porcelanato retificado 60x60</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E63" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F63" s="63" t="n"/>
+      <c r="G63" s="63" t="n"/>
+      <c r="H63" s="63" t="n"/>
+      <c r="I63" s="63" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="64" t="inlineStr"/>
+      <c r="B64" s="65" t="inlineStr"/>
+      <c r="C64" s="66" t="n"/>
+      <c r="D64" s="66" t="n"/>
+      <c r="E64" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F64" s="67" t="inlineStr">
+        <is>
+          <t>87261</t>
+        </is>
+      </c>
+      <c r="G64" s="68" t="inlineStr">
+        <is>
+          <t>REVESTIMENTO CERÂMICO PARA PISO COM PLACAS TIPO PORCELANATO DE DIMENSÕES 60X60 CM APLICADA EM A</t>
+        </is>
+      </c>
+      <c r="H64" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I64" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="64" t="inlineStr"/>
+      <c r="B65" s="65" t="inlineStr"/>
+      <c r="C65" s="66" t="n"/>
+      <c r="D65" s="66" t="n"/>
+      <c r="E65" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F65" s="67" t="inlineStr">
+        <is>
+          <t>~101735</t>
+        </is>
+      </c>
+      <c r="G65" s="68" t="inlineStr">
+        <is>
+          <t>PISO DE BORRACHA ESPORTIVO, ESPESSURA 15MM, ASSENTADO COM ARGAMASSA. AF_02/2026</t>
+        </is>
+      </c>
+      <c r="H65" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I65" s="67" t="inlineStr">
+        <is>
+          <t>15% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="61" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>Rodapé em porcelanato h=7cm</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="E67" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F67" s="63" t="n"/>
+      <c r="G67" s="63" t="n"/>
+      <c r="H67" s="63" t="n"/>
+      <c r="I67" s="63" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="64" t="inlineStr"/>
+      <c r="B68" s="65" t="inlineStr"/>
+      <c r="C68" s="66" t="n"/>
+      <c r="D68" s="66" t="n"/>
+      <c r="E68" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F68" s="67" t="inlineStr">
+        <is>
+          <t>~88650</t>
+        </is>
+      </c>
+      <c r="G68" s="68" t="inlineStr">
+        <is>
+          <t>RODAPÉ CERÂMICO DE 7CM DE ALTURA COM PLACAS TIPO ESMALTADA DE DIMENSÕES 60X60CM. AF_02/2023</t>
+        </is>
+      </c>
+      <c r="H68" s="69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I68" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="64" t="inlineStr"/>
+      <c r="B69" s="65" t="inlineStr"/>
+      <c r="C69" s="66" t="n"/>
+      <c r="D69" s="66" t="n"/>
+      <c r="E69" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F69" s="67" t="inlineStr">
+        <is>
+          <t>~104619</t>
+        </is>
+      </c>
+      <c r="G69" s="68" t="inlineStr">
+        <is>
+          <t>RODAPÉ CERÂMICO DE 7CM DE ALTURA COM PLACAS TIPO ESMALTADA DE DIMENSÕES 80X80CM. AF_02/2023</t>
+        </is>
+      </c>
+      <c r="H69" s="69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I69" s="67" t="inlineStr">
+        <is>
+          <t>27% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="61" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B71" s="43" t="inlineStr">
+        <is>
+          <t>Piso vinílico em manta (sala de reunião)</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E71" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F71" s="63" t="n"/>
+      <c r="G71" s="63" t="n"/>
+      <c r="H71" s="63" t="n"/>
+      <c r="I71" s="63" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="64" t="inlineStr"/>
+      <c r="B72" s="65" t="inlineStr"/>
+      <c r="C72" s="66" t="n"/>
+      <c r="D72" s="66" t="n"/>
+      <c r="E72" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F72" s="67" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="G72" s="68" t="inlineStr">
+        <is>
+          <t>PISO VINÍLICO FLEXÍVEL EM MANTA, PADRÃO LISO, ESPESSURA 2 MM, FIXADO COM COLA. AF_02/2026</t>
+        </is>
+      </c>
+      <c r="H72" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I72" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="64" t="inlineStr"/>
+      <c r="B73" s="65" t="inlineStr"/>
+      <c r="C73" s="66" t="n"/>
+      <c r="D73" s="66" t="n"/>
+      <c r="E73" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F73" s="67" t="inlineStr">
+        <is>
+          <t>~101735</t>
+        </is>
+      </c>
+      <c r="G73" s="68" t="inlineStr">
+        <is>
+          <t>PISO DE BORRACHA ESPORTIVO, ESPESSURA 15MM, ASSENTADO COM ARGAMASSA. AF_02/2026</t>
+        </is>
+      </c>
+      <c r="H73" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I73" s="67" t="inlineStr">
+        <is>
+          <t>20% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="61" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="inlineStr">
+        <is>
+          <t>Pintura látex acrílica em parede (2 demãos)</t>
+        </is>
+      </c>
+      <c r="C75" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>214</v>
+      </c>
+      <c r="E75" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F75" s="63" t="n"/>
+      <c r="G75" s="63" t="n"/>
+      <c r="H75" s="63" t="n"/>
+      <c r="I75" s="63" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="64" t="inlineStr"/>
+      <c r="B76" s="65" t="inlineStr"/>
+      <c r="C76" s="66" t="n"/>
+      <c r="D76" s="66" t="n"/>
+      <c r="E76" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F76" s="67" t="inlineStr">
+        <is>
+          <t>~88489</t>
+        </is>
+      </c>
+      <c r="G76" s="68" t="inlineStr">
+        <is>
+          <t>PINTURA LÁTEX ACRÍLICA PREMIUM, APLICAÇÃO MANUAL EM PAREDES, DUAS DEMÃOS. AF_04/2023</t>
+        </is>
+      </c>
+      <c r="H76" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I76" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="64" t="inlineStr"/>
+      <c r="B77" s="65" t="inlineStr"/>
+      <c r="C77" s="66" t="n"/>
+      <c r="D77" s="66" t="n"/>
+      <c r="E77" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F77" s="67" t="inlineStr">
+        <is>
+          <t>~102491</t>
+        </is>
+      </c>
+      <c r="G77" s="68" t="inlineStr">
+        <is>
+          <t>PINTURA DE PISO COM TINTA ACRÍLICA, APLICAÇÃO MANUAL, 2 DEMÃOS, INCLUSO FUNDO PREPARADOR. AF_05</t>
+        </is>
+      </c>
+      <c r="H77" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I77" s="67" t="inlineStr">
+        <is>
+          <t>40% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="57" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B79" s="58" t="inlineStr">
+        <is>
+          <t>Pintura em forro de gesso</t>
+        </is>
+      </c>
+      <c r="C79" s="57" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D79" s="57" t="n">
         <v>101.7</v>
       </c>
-      <c r="E46" s="58" t="inlineStr">
+      <c r="E79" s="59" t="inlineStr">
+        <is>
+          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
+        </is>
+      </c>
+      <c r="F79" s="60" t="n"/>
+      <c r="G79" s="60" t="n"/>
+      <c r="H79" s="60" t="n"/>
+      <c r="I79" s="60" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="61" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B80" s="43" t="inlineStr">
+        <is>
+          <t>Porta de madeira 80x210 com batente e ferragens</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F46" s="59" t="n"/>
-      <c r="G46" s="59" t="n"/>
-      <c r="H46" s="59" t="n"/>
-      <c r="I46" s="59" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="60" t="inlineStr"/>
-      <c r="B47" s="61" t="inlineStr"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="63" t="inlineStr">
+      <c r="F80" s="63" t="n"/>
+      <c r="G80" s="63" t="n"/>
+      <c r="H80" s="63" t="n"/>
+      <c r="I80" s="63" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="64" t="inlineStr"/>
+      <c r="B81" s="65" t="inlineStr"/>
+      <c r="C81" s="66" t="n"/>
+      <c r="D81" s="66" t="n"/>
+      <c r="E81" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F47" s="63" t="inlineStr">
-        <is>
-          <t>106129</t>
-        </is>
-      </c>
-      <c r="G47" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REMOÇÃO DE ENTULHO CLASSE B (PEÇAS MAIORES DE GESSO ACARTONADO) TRANSPORTADOS POR CREMALHEIRA. </t>
-        </is>
-      </c>
-      <c r="H47" s="65" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="I47" s="63" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="57" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B49" s="43" t="inlineStr">
-        <is>
-          <t>Sanca de gesso perimetral</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="n">
-        <v>46</v>
-      </c>
-      <c r="E49" s="58" t="inlineStr">
+      <c r="F81" s="67" t="inlineStr">
+        <is>
+          <t>91297</t>
+        </is>
+      </c>
+      <c r="G81" s="68" t="inlineStr">
+        <is>
+          <t>PORTA DE MADEIRA FRISADA, SEMI-OCA (LEVE OU MÉDIA), 80X210CM, ESPESSURA DE 3,5CM, INCLUSO DOBRA</t>
+        </is>
+      </c>
+      <c r="H81" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I81" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="64" t="inlineStr"/>
+      <c r="B82" s="65" t="inlineStr"/>
+      <c r="C82" s="66" t="n"/>
+      <c r="D82" s="66" t="n"/>
+      <c r="E82" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F82" s="67" t="inlineStr">
+        <is>
+          <t>~106319</t>
+        </is>
+      </c>
+      <c r="G82" s="68" t="inlineStr">
+        <is>
+          <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 80X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
+        </is>
+      </c>
+      <c r="H82" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I82" s="67" t="inlineStr">
+        <is>
+          <t>25% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="61" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="B84" s="43" t="inlineStr">
+        <is>
+          <t>Porta de vidro temperado 90x210</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F49" s="59" t="n"/>
-      <c r="G49" s="59" t="n"/>
-      <c r="H49" s="59" t="n"/>
-      <c r="I49" s="59" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="60" t="inlineStr"/>
-      <c r="B50" s="61" t="inlineStr"/>
-      <c r="C50" s="62" t="n"/>
-      <c r="D50" s="62" t="n"/>
-      <c r="E50" s="63" t="inlineStr">
+      <c r="F84" s="63" t="n"/>
+      <c r="G84" s="63" t="n"/>
+      <c r="H84" s="63" t="n"/>
+      <c r="I84" s="63" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="64" t="inlineStr"/>
+      <c r="B85" s="65" t="inlineStr"/>
+      <c r="C85" s="66" t="n"/>
+      <c r="D85" s="66" t="n"/>
+      <c r="E85" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F50" s="63" t="inlineStr">
-        <is>
-          <t>~99054</t>
-        </is>
-      </c>
-      <c r="G50" s="64" t="inlineStr">
-        <is>
-          <t>ACABAMENTOS PARA FORRO (SANCA DE GESSO, MONTADA NA OBRA). AF_08/2023_PS</t>
-        </is>
-      </c>
-      <c r="H50" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I50" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="60" t="inlineStr"/>
-      <c r="B51" s="61" t="inlineStr"/>
-      <c r="C51" s="62" t="n"/>
-      <c r="D51" s="62" t="n"/>
-      <c r="E51" s="63" t="inlineStr">
+      <c r="F85" s="67" t="inlineStr">
+        <is>
+          <t>102184</t>
+        </is>
+      </c>
+      <c r="G85" s="68" t="inlineStr">
+        <is>
+          <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 90X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
+        </is>
+      </c>
+      <c r="H85" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I85" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="64" t="inlineStr"/>
+      <c r="B86" s="65" t="inlineStr"/>
+      <c r="C86" s="66" t="n"/>
+      <c r="D86" s="66" t="n"/>
+      <c r="E86" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F51" s="63" t="inlineStr">
-        <is>
-          <t>~86904</t>
-        </is>
-      </c>
-      <c r="G51" s="64" t="inlineStr">
-        <is>
-          <t>LAVATÓRIO LOUÇA BRANCA SUSPENSO, *40 X 30* CM OU EQUIVALENTE, PADRÃO POPULAR - FORNECIMENTO E I</t>
-        </is>
-      </c>
-      <c r="H51" s="65" t="inlineStr">
+      <c r="F86" s="67" t="inlineStr">
+        <is>
+          <t>~106319</t>
+        </is>
+      </c>
+      <c r="G86" s="68" t="inlineStr">
+        <is>
+          <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 80X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
+        </is>
+      </c>
+      <c r="H86" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I51" s="63" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="57" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="inlineStr">
-        <is>
-          <t>Pintura látex acrílica em parede (2 demãos)</t>
-        </is>
-      </c>
-      <c r="C53" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D53" s="23" t="n">
-        <v>214</v>
-      </c>
-      <c r="E53" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F53" s="59" t="n"/>
-      <c r="G53" s="59" t="n"/>
-      <c r="H53" s="59" t="n"/>
-      <c r="I53" s="59" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="60" t="inlineStr"/>
-      <c r="B54" s="61" t="inlineStr"/>
-      <c r="C54" s="62" t="n"/>
-      <c r="D54" s="62" t="n"/>
-      <c r="E54" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F54" s="63" t="inlineStr">
-        <is>
-          <t>95626</t>
-        </is>
-      </c>
-      <c r="G54" s="64" t="inlineStr">
-        <is>
-          <t>APLICAÇÃO MANUAL DE TINTA LÁTEX ACRÍLICA EM PAREDE EXTERNAS DE CASAS, DUAS DEMÃOS. AF_03/2024</t>
-        </is>
-      </c>
-      <c r="H54" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I54" s="63" t="inlineStr">
-        <is>
-          <t>63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="57" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B56" s="43" t="inlineStr">
-        <is>
-          <t>Pintura em forro de gesso</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D56" s="23" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="E56" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F56" s="59" t="n"/>
-      <c r="G56" s="59" t="n"/>
-      <c r="H56" s="59" t="n"/>
-      <c r="I56" s="59" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="60" t="inlineStr"/>
-      <c r="B57" s="61" t="inlineStr"/>
-      <c r="C57" s="62" t="n"/>
-      <c r="D57" s="62" t="n"/>
-      <c r="E57" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F57" s="63" t="inlineStr">
-        <is>
-          <t>~102232</t>
-        </is>
-      </c>
-      <c r="G57" s="64" t="inlineStr">
-        <is>
-          <t>PINTURA TINTA DE ACABAMENTO (PIGMENTADA) POLIURETÂNICA EM MADEIRA, 3 DEMÃOS. AF_01/2021</t>
-        </is>
-      </c>
-      <c r="H57" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I57" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="60" t="inlineStr"/>
-      <c r="B58" s="61" t="inlineStr"/>
-      <c r="C58" s="62" t="n"/>
-      <c r="D58" s="62" t="n"/>
-      <c r="E58" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F58" s="63" t="inlineStr">
-        <is>
-          <t>~102198</t>
-        </is>
-      </c>
-      <c r="G58" s="64" t="inlineStr">
-        <is>
-          <t>PINTURA FUNDO NIVELADOR ACRÍLICO BRANCO EM MADEIRA. AF_01/2021</t>
-        </is>
-      </c>
-      <c r="H58" s="65" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I58" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="57" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B60" s="43" t="inlineStr">
-        <is>
-          <t>Porta de madeira 80x210 com batente e ferragens</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D60" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F60" s="59" t="n"/>
-      <c r="G60" s="59" t="n"/>
-      <c r="H60" s="59" t="n"/>
-      <c r="I60" s="59" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="60" t="inlineStr"/>
-      <c r="B61" s="61" t="inlineStr"/>
-      <c r="C61" s="62" t="n"/>
-      <c r="D61" s="62" t="n"/>
-      <c r="E61" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F61" s="63" t="inlineStr">
-        <is>
-          <t>~105472</t>
-        </is>
-      </c>
-      <c r="G61" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CARGA E DESCARGA MANUAL, DE JANELA, KIT PORTA-PRONTA OU PORTA DE MADEIRA, PORTA DE AÇO E PORTA </t>
-        </is>
-      </c>
-      <c r="H61" s="65" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I61" s="63" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="60" t="inlineStr"/>
-      <c r="B62" s="61" t="inlineStr"/>
-      <c r="C62" s="62" t="n"/>
-      <c r="D62" s="62" t="n"/>
-      <c r="E62" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F62" s="63" t="inlineStr">
-        <is>
-          <t>~105413</t>
-        </is>
-      </c>
-      <c r="G62" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CARGA E DESCARGA MANUAL, DE JANELA, KIT PORTA-PRONTA OU PORTA DE MADEIRA, PORTA DE AÇO E PORTA </t>
-        </is>
-      </c>
-      <c r="H62" s="65" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I62" s="63" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="57" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B64" s="43" t="inlineStr">
-        <is>
-          <t>Porta de vidro temperado 90x210</t>
-        </is>
-      </c>
-      <c r="C64" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D64" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E64" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F64" s="59" t="n"/>
-      <c r="G64" s="59" t="n"/>
-      <c r="H64" s="59" t="n"/>
-      <c r="I64" s="59" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="60" t="inlineStr"/>
-      <c r="B65" s="61" t="inlineStr"/>
-      <c r="C65" s="62" t="n"/>
-      <c r="D65" s="62" t="n"/>
-      <c r="E65" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F65" s="63" t="inlineStr">
-        <is>
-          <t>102182</t>
-        </is>
-      </c>
-      <c r="G65" s="64" t="inlineStr">
-        <is>
-          <t>PORTA PIVOTANTE DE VIDRO TEMPERADO, 90X210 CM, ESPESSURA 10 MM, INCLUSIVE ACESSÓRIOS. AF_11/202</t>
-        </is>
-      </c>
-      <c r="H65" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I65" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="60" t="inlineStr"/>
-      <c r="B66" s="61" t="inlineStr"/>
-      <c r="C66" s="62" t="n"/>
-      <c r="D66" s="62" t="n"/>
-      <c r="E66" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F66" s="63" t="inlineStr">
-        <is>
-          <t>102186</t>
-        </is>
-      </c>
-      <c r="G66" s="64" t="inlineStr">
-        <is>
-          <t>PORTA DE CORRER EM VIDRO TEMPERADO, 90X210 CM, ESPESSURA 10 MM, INCLUSIVE ACESSÓRIOS. AF_11/202</t>
-        </is>
-      </c>
-      <c r="H66" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I66" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="57" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B68" s="43" t="inlineStr">
-        <is>
-          <t>Luminária LED de embutir 60x60</t>
-        </is>
-      </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D68" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="E68" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F68" s="59" t="n"/>
-      <c r="G68" s="59" t="n"/>
-      <c r="H68" s="59" t="n"/>
-      <c r="I68" s="59" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="60" t="inlineStr"/>
-      <c r="B69" s="61" t="inlineStr"/>
-      <c r="C69" s="62" t="n"/>
-      <c r="D69" s="62" t="n"/>
-      <c r="E69" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F69" s="63" t="inlineStr">
-        <is>
-          <t>105542</t>
-        </is>
-      </c>
-      <c r="G69" s="64" t="inlineStr">
-        <is>
-          <t>LUMINÁRIA LED DE EMBUTIR - QUADRADA 60X60CM, INCLUSO DRIVER - FORNECIMENTO E INSTALAÇÃO. AF_09/</t>
-        </is>
-      </c>
-      <c r="H69" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I69" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="57" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B71" s="43" t="inlineStr">
-        <is>
-          <t>Spot LED de embutir redondo</t>
-        </is>
-      </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D71" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="E71" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F71" s="59" t="n"/>
-      <c r="G71" s="59" t="n"/>
-      <c r="H71" s="59" t="n"/>
-      <c r="I71" s="59" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="60" t="inlineStr"/>
-      <c r="B72" s="61" t="inlineStr"/>
-      <c r="C72" s="62" t="n"/>
-      <c r="D72" s="62" t="n"/>
-      <c r="E72" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F72" s="63" t="inlineStr">
-        <is>
-          <t>106773</t>
-        </is>
-      </c>
-      <c r="G72" s="64" t="inlineStr">
-        <is>
-          <t>CUBA DE EMBUTIR REDONDA EM LOUÇA BRANCA, 36 CM OU EQUIVALENTE - FORNECIMENTO E INSTALAÇÃO. AF_0</t>
-        </is>
-      </c>
-      <c r="H72" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I72" s="63" t="inlineStr">
-        <is>
-          <t>63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="57" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="B74" s="43" t="inlineStr">
-        <is>
-          <t>Pendente decorativo sobre bancada</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D74" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E74" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F74" s="59" t="n"/>
-      <c r="G74" s="59" t="n"/>
-      <c r="H74" s="59" t="n"/>
-      <c r="I74" s="59" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="60" t="inlineStr"/>
-      <c r="B75" s="61" t="inlineStr"/>
-      <c r="C75" s="62" t="n"/>
-      <c r="D75" s="62" t="n"/>
-      <c r="E75" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F75" s="63" t="inlineStr">
-        <is>
-          <t>~95696</t>
-        </is>
-      </c>
-      <c r="G75" s="64" t="inlineStr">
-        <is>
-          <t>SPRINKLER TIPO PENDENTE, 68 °C, UNIÃO POR ROSCA DN 15 (1/2") - FORNECIMENTO E INSTALAÇÃO. AF_01</t>
-        </is>
-      </c>
-      <c r="H75" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I75" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="57" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B77" s="43" t="inlineStr">
-        <is>
-          <t>Ponto de tomada 2P+T 10A</t>
-        </is>
-      </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D77" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="E77" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F77" s="59" t="n"/>
-      <c r="G77" s="59" t="n"/>
-      <c r="H77" s="59" t="n"/>
-      <c r="I77" s="59" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="60" t="inlineStr"/>
-      <c r="B78" s="61" t="inlineStr"/>
-      <c r="C78" s="62" t="n"/>
-      <c r="D78" s="62" t="n"/>
-      <c r="E78" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F78" s="63" t="inlineStr">
-        <is>
-          <t>~92010</t>
-        </is>
-      </c>
-      <c r="G78" s="64" t="inlineStr">
-        <is>
-          <t>TOMADA MÉDIA DE EMBUTIR (3 MÓDULOS), 2P+T 10 A, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTAL</t>
-        </is>
-      </c>
-      <c r="H78" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I78" s="63" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="60" t="inlineStr"/>
-      <c r="B79" s="61" t="inlineStr"/>
-      <c r="C79" s="62" t="n"/>
-      <c r="D79" s="62" t="n"/>
-      <c r="E79" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F79" s="63" t="inlineStr">
-        <is>
-          <t>~91990</t>
-        </is>
-      </c>
-      <c r="G79" s="64" t="inlineStr">
-        <is>
-          <t>TOMADA ALTA DE EMBUTIR (1 MÓDULO), 2P+T 10 A, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇ</t>
-        </is>
-      </c>
-      <c r="H79" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I79" s="63" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="57" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B81" s="43" t="inlineStr">
-        <is>
-          <t>Ponto de interruptor</t>
-        </is>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D81" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="E81" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F81" s="59" t="n"/>
-      <c r="G81" s="59" t="n"/>
-      <c r="H81" s="59" t="n"/>
-      <c r="I81" s="59" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="60" t="inlineStr"/>
-      <c r="B82" s="61" t="inlineStr"/>
-      <c r="C82" s="62" t="n"/>
-      <c r="D82" s="62" t="n"/>
-      <c r="E82" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F82" s="63" t="inlineStr">
-        <is>
-          <t>91955</t>
-        </is>
-      </c>
-      <c r="G82" s="64" t="inlineStr">
-        <is>
-          <t>INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃ</t>
-        </is>
-      </c>
-      <c r="H82" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I82" s="63" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="60" t="inlineStr"/>
-      <c r="B83" s="61" t="inlineStr"/>
-      <c r="C83" s="62" t="n"/>
-      <c r="D83" s="62" t="n"/>
-      <c r="E83" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F83" s="63" t="inlineStr">
-        <is>
-          <t>91954</t>
-        </is>
-      </c>
-      <c r="G83" s="64" t="inlineStr">
-        <is>
-          <t>INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇÃO.</t>
-        </is>
-      </c>
-      <c r="H83" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I83" s="63" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="66" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B85" s="67" t="inlineStr">
-        <is>
-          <t>Ponto de rede/dados RJ45 cat6</t>
-        </is>
-      </c>
-      <c r="C85" s="66" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D85" s="66" t="n">
-        <v>20</v>
-      </c>
-      <c r="E85" s="68" t="inlineStr">
-        <is>
-          <t>Sem match SINAPI (descrição muito específica) — buscar manualmente em https://www.caixa.gov.br/sinapi</t>
-        </is>
-      </c>
-      <c r="F85" s="69" t="n"/>
-      <c r="G85" s="69" t="n"/>
-      <c r="H85" s="69" t="n"/>
-      <c r="I85" s="69" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="57" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B86" s="43" t="inlineStr">
-        <is>
-          <t>Ar-condicionado split cassete 36.000 BTU</t>
-        </is>
-      </c>
-      <c r="C86" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D86" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F86" s="59" t="n"/>
-      <c r="G86" s="59" t="n"/>
-      <c r="H86" s="59" t="n"/>
-      <c r="I86" s="59" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="60" t="inlineStr"/>
-      <c r="B87" s="61" t="inlineStr"/>
-      <c r="C87" s="62" t="n"/>
-      <c r="D87" s="62" t="n"/>
-      <c r="E87" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F87" s="63" t="inlineStr">
-        <is>
-          <t>103272</t>
-        </is>
-      </c>
-      <c r="G87" s="64" t="inlineStr">
-        <is>
-          <t>AR CONDICIONADO SPLIT ON/OFF, CASSETE (TETO), 36000 BTU/H, CICLO QUENTE/FRIO - FORNECIMENTO E I</t>
-        </is>
-      </c>
-      <c r="H87" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I87" s="63" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="60" t="inlineStr"/>
-      <c r="B88" s="61" t="inlineStr"/>
-      <c r="C88" s="62" t="n"/>
-      <c r="D88" s="62" t="n"/>
-      <c r="E88" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F88" s="63" t="inlineStr">
-        <is>
-          <t>103276</t>
-        </is>
-      </c>
-      <c r="G88" s="64" t="inlineStr">
-        <is>
-          <t>AR CONDICIONADO SPLIT ON/OFF, CASSETE (TETO), 60000 BTU/H, CICLO QUENTE/FRIO - FORNECIMENTO E I</t>
-        </is>
-      </c>
-      <c r="H88" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I88" s="63" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="57" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B90" s="43" t="inlineStr">
-        <is>
-          <t>Bacia sanitária com caixa acoplada</t>
-        </is>
-      </c>
-      <c r="C90" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D90" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F90" s="59" t="n"/>
-      <c r="G90" s="59" t="n"/>
-      <c r="H90" s="59" t="n"/>
-      <c r="I90" s="59" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="60" t="inlineStr"/>
-      <c r="B91" s="61" t="inlineStr"/>
-      <c r="C91" s="62" t="n"/>
-      <c r="D91" s="62" t="n"/>
-      <c r="E91" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F91" s="63" t="inlineStr">
-        <is>
-          <t>86888</t>
-        </is>
-      </c>
-      <c r="G91" s="64" t="inlineStr">
-        <is>
-          <t>BACIA SANITÁRIA COM CAIXA ACOPLADA LOUÇA BRANCA - FORNECIMENTO E INSTALAÇÃO. AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H91" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I91" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="60" t="inlineStr"/>
-      <c r="B92" s="61" t="inlineStr"/>
-      <c r="C92" s="62" t="n"/>
-      <c r="D92" s="62" t="n"/>
-      <c r="E92" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F92" s="63" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="G92" s="64" t="inlineStr">
-        <is>
-          <t>BACIA SANITÁRIA COM CAIXA ACOPLADA, LOUÇA BRANCA - PADRÃO ALTO - FORNECIMENTO E INSTALAÇÃO. AF_</t>
-        </is>
-      </c>
-      <c r="H92" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I92" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="57" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B94" s="43" t="inlineStr">
-        <is>
-          <t>Cuba de apoio + torneira (copa)</t>
-        </is>
-      </c>
-      <c r="C94" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D94" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="58" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F94" s="59" t="n"/>
-      <c r="G94" s="59" t="n"/>
-      <c r="H94" s="59" t="n"/>
-      <c r="I94" s="59" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="60" t="inlineStr"/>
-      <c r="B95" s="61" t="inlineStr"/>
-      <c r="C95" s="62" t="n"/>
-      <c r="D95" s="62" t="n"/>
-      <c r="E95" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F95" s="63" t="inlineStr">
-        <is>
-          <t>~106773</t>
-        </is>
-      </c>
-      <c r="G95" s="64" t="inlineStr">
-        <is>
-          <t>CUBA DE EMBUTIR REDONDA EM LOUÇA BRANCA, 36 CM OU EQUIVALENTE - FORNECIMENTO E INSTALAÇÃO. AF_0</t>
-        </is>
-      </c>
-      <c r="H95" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I95" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="60" t="inlineStr"/>
-      <c r="B96" s="61" t="inlineStr"/>
-      <c r="C96" s="62" t="n"/>
-      <c r="D96" s="62" t="n"/>
-      <c r="E96" s="63" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F96" s="63" t="inlineStr">
-        <is>
-          <t>~100852</t>
-        </is>
-      </c>
-      <c r="G96" s="64" t="inlineStr">
-        <is>
-          <t>CUBA DE EMBUTIR RETANGULAR DE AÇO INOXIDÁVEL, 56 X 33 X 12 CM - FORNECIMENTO E INSTALAÇÃO. AF_0</t>
-        </is>
-      </c>
-      <c r="H96" s="65" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I96" s="63" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="inlineStr">
+      <c r="I86" s="67" t="inlineStr">
+        <is>
+          <t>57% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>Como ler: MATCH % indica a similaridade entre a descrição do item e a composição SINAPI. Acima de 70% = referência forte. 40-70% = revisar. Abaixo de 30% = candidato fraco, buscar código manualmente em https://www.caixa.gov.br/sinapi.</t>
         </is>
@@ -5779,35 +5624,35 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="E68:I68"/>
-    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="E55:I55"/>
+    <mergeCell ref="A89:I89"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="E71:I71"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="E64:I64"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="E79:I79"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E51:I51"/>
     <mergeCell ref="E38:I38"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="E94:I94"/>
-    <mergeCell ref="E60:I60"/>
-    <mergeCell ref="E74:I74"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="E63:I63"/>
+    <mergeCell ref="E84:I84"/>
     <mergeCell ref="E30:I30"/>
     <mergeCell ref="E34:I34"/>
-    <mergeCell ref="E90:I90"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E6:I6"/>
-    <mergeCell ref="E22:I22"/>
-    <mergeCell ref="E77:I77"/>
     <mergeCell ref="E46:I46"/>
-    <mergeCell ref="E86:I86"/>
-    <mergeCell ref="E49:I49"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="E26:I26"/>
-    <mergeCell ref="E85:I85"/>
-    <mergeCell ref="E81:I81"/>
+    <mergeCell ref="E80:I80"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E25:I25"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="E53:I53"/>
-    <mergeCell ref="E56:I56"/>
+    <mergeCell ref="E75:I75"/>
+    <mergeCell ref="E47:I47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/exemplos/quantitativo-exemplo-aiarq.xlsx
+++ b/exemplos/quantitativo-exemplo-aiarq.xlsx
@@ -817,7 +817,7 @@
     <row r="1" ht="48" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Quantitativo gerado por IA. NÃO é orçamento. Revisão por arquiteto ou engenheiro habilitado é obrigatória antes do uso. Itens em LARANJA são sugestões da IA — confira contra o projeto antes de mandar pros fornecedores.</t>
+          <t>⚠️ O AI.arq é uma IA e pode cometer erros — confira as informações importantes. Quantitativo gerado por IA, NÃO é orçamento. Revisão por arquiteto ou engenheiro habilitado é obrigatória antes do uso. Itens em LARANJA são sugestões da IA — confira contra o projeto antes de mandar pros fornecedores.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>SINAPI: sem correspondência forte (ver aba técnica)</t>
+          <t>SINAPI ~97638 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I28" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~92004 (conf. alta)</t>
+          <t>SINAPI 91996 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I29" s="22" t="inlineStr">
         <is>
-          <t>SINAPI ~91953 (conf. alta)</t>
+          <t>SINAPI ~91952 (conf. alta)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3862,62 +3862,64 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>Remoção de divisória existente</t>
         </is>
       </c>
-      <c r="C12" s="57" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D12" s="57" t="n">
+      <c r="D12" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
-        </is>
-      </c>
-      <c r="F12" s="60" t="n"/>
-      <c r="G12" s="60" t="n"/>
-      <c r="H12" s="60" t="n"/>
-      <c r="I12" s="60" t="n"/>
+      <c r="E12" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F12" s="63" t="n"/>
+      <c r="G12" s="63" t="n"/>
+      <c r="H12" s="63" t="n"/>
+      <c r="I12" s="63" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>Forro de gesso acartonado liso</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="E13" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F13" s="63" t="n"/>
-      <c r="G13" s="63" t="n"/>
-      <c r="H13" s="63" t="n"/>
-      <c r="I13" s="63" t="n"/>
+      <c r="A13" s="64" t="inlineStr"/>
+      <c r="B13" s="65" t="inlineStr"/>
+      <c r="C13" s="66" t="n"/>
+      <c r="D13" s="66" t="n"/>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>~97638</t>
+        </is>
+      </c>
+      <c r="G13" s="68" t="inlineStr">
+        <is>
+          <t>REMOÇÃO DE CHAPAS E PERFIS DE DRYWALL, DE FORMA MANUAL, SEM REAPROVEITAMENTO. AF_09/2023</t>
+        </is>
+      </c>
+      <c r="H13" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I13" s="67" t="inlineStr">
+        <is>
+          <t>✓ IA conferiu</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="64" t="inlineStr"/>
@@ -3931,84 +3933,84 @@
       </c>
       <c r="F14" s="67" t="inlineStr">
         <is>
+          <t>~97660</t>
+        </is>
+      </c>
+      <c r="G14" s="68" t="inlineStr">
+        <is>
+          <t>REMOÇÃO DE INTERRUPTORES/TOMADAS ELÉTRICAS, DE FORMA MANUAL, SEM REAPROVEITAMENTO. AF_09/2023</t>
+        </is>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I14" s="67" t="inlineStr">
+        <is>
+          <t>36% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="61" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Forro de gesso acartonado liso</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="E16" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F16" s="63" t="n"/>
+      <c r="G16" s="63" t="n"/>
+      <c r="H16" s="63" t="n"/>
+      <c r="I16" s="63" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="64" t="inlineStr"/>
+      <c r="B17" s="65" t="inlineStr"/>
+      <c r="C17" s="66" t="n"/>
+      <c r="D17" s="66" t="n"/>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
           <t>~96114</t>
         </is>
       </c>
-      <c r="G14" s="68" t="inlineStr">
+      <c r="G17" s="68" t="inlineStr">
         <is>
           <t>FORRO EM DRYWALL, PARA AMBIENTES COMERCIAIS, INCLUSIVE ESTRUTURA BIRECIONAL DE FIXAÇÃO. AF_08/2</t>
         </is>
       </c>
-      <c r="H14" s="69" t="inlineStr">
+      <c r="H17" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I14" s="67" t="inlineStr">
+      <c r="I17" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="64" t="inlineStr"/>
-      <c r="B15" s="65" t="inlineStr"/>
-      <c r="C15" s="66" t="n"/>
-      <c r="D15" s="66" t="n"/>
-      <c r="E15" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F15" s="67" t="inlineStr">
-        <is>
-          <t>~96113</t>
-        </is>
-      </c>
-      <c r="G15" s="68" t="inlineStr">
-        <is>
-          <t>FORRO EM PLACAS DE GESSO, PARA AMBIENTES COMERCIAIS. AF_08/2023_PS</t>
-        </is>
-      </c>
-      <c r="H15" s="69" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I15" s="67" t="inlineStr">
-        <is>
-          <t>41% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="61" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>Sanca de gesso perimetral</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="n">
-        <v>46</v>
-      </c>
-      <c r="E17" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F17" s="63" t="n"/>
-      <c r="G17" s="63" t="n"/>
-      <c r="H17" s="63" t="n"/>
-      <c r="I17" s="63" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="64" t="inlineStr"/>
@@ -4022,84 +4024,84 @@
       </c>
       <c r="F18" s="67" t="inlineStr">
         <is>
+          <t>~96113</t>
+        </is>
+      </c>
+      <c r="G18" s="68" t="inlineStr">
+        <is>
+          <t>FORRO EM PLACAS DE GESSO, PARA AMBIENTES COMERCIAIS. AF_08/2023_PS</t>
+        </is>
+      </c>
+      <c r="H18" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I18" s="67" t="inlineStr">
+        <is>
+          <t>41% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="61" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Sanca de gesso perimetral</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="E20" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="n"/>
+      <c r="G20" s="63" t="n"/>
+      <c r="H20" s="63" t="n"/>
+      <c r="I20" s="63" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="64" t="inlineStr"/>
+      <c r="B21" s="65" t="inlineStr"/>
+      <c r="C21" s="66" t="n"/>
+      <c r="D21" s="66" t="n"/>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
           <t>99054</t>
         </is>
       </c>
-      <c r="G18" s="68" t="inlineStr">
+      <c r="G21" s="68" t="inlineStr">
         <is>
           <t>ACABAMENTOS PARA FORRO (SANCA DE GESSO, MONTADA NA OBRA). AF_08/2023_PS</t>
         </is>
       </c>
-      <c r="H18" s="69" t="inlineStr">
+      <c r="H21" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I18" s="67" t="inlineStr">
+      <c r="I21" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="64" t="inlineStr"/>
-      <c r="B19" s="65" t="inlineStr"/>
-      <c r="C19" s="66" t="n"/>
-      <c r="D19" s="66" t="n"/>
-      <c r="E19" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F19" s="67" t="inlineStr">
-        <is>
-          <t>~86904</t>
-        </is>
-      </c>
-      <c r="G19" s="68" t="inlineStr">
-        <is>
-          <t>LAVATÓRIO LOUÇA BRANCA SUSPENSO, *40 X 30* CM OU EQUIVALENTE, PADRÃO POPULAR - FORNECIMENTO E I</t>
-        </is>
-      </c>
-      <c r="H19" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I19" s="67" t="inlineStr">
-        <is>
-          <t>15% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="61" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>Luminária LED de embutir 60x60</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="E21" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F21" s="63" t="n"/>
-      <c r="G21" s="63" t="n"/>
-      <c r="H21" s="63" t="n"/>
-      <c r="I21" s="63" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="64" t="inlineStr"/>
@@ -4113,84 +4115,84 @@
       </c>
       <c r="F22" s="67" t="inlineStr">
         <is>
+          <t>~86904</t>
+        </is>
+      </c>
+      <c r="G22" s="68" t="inlineStr">
+        <is>
+          <t>LAVATÓRIO LOUÇA BRANCA SUSPENSO, *40 X 30* CM OU EQUIVALENTE, PADRÃO POPULAR - FORNECIMENTO E I</t>
+        </is>
+      </c>
+      <c r="H22" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I22" s="67" t="inlineStr">
+        <is>
+          <t>15% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Luminária LED de embutir 60x60</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="n"/>
+      <c r="G24" s="63" t="n"/>
+      <c r="H24" s="63" t="n"/>
+      <c r="I24" s="63" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="64" t="inlineStr"/>
+      <c r="B25" s="65" t="inlineStr"/>
+      <c r="C25" s="66" t="n"/>
+      <c r="D25" s="66" t="n"/>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
           <t>105542</t>
         </is>
       </c>
-      <c r="G22" s="68" t="inlineStr">
+      <c r="G25" s="68" t="inlineStr">
         <is>
           <t>LUMINÁRIA LED DE EMBUTIR - QUADRADA 60X60CM, INCLUSO DRIVER - FORNECIMENTO E INSTALAÇÃO. AF_09/</t>
         </is>
       </c>
-      <c r="H22" s="69" t="inlineStr">
+      <c r="H25" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I22" s="67" t="inlineStr">
+      <c r="I25" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="64" t="inlineStr"/>
-      <c r="B23" s="65" t="inlineStr"/>
-      <c r="C23" s="66" t="n"/>
-      <c r="D23" s="66" t="n"/>
-      <c r="E23" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F23" s="67" t="inlineStr">
-        <is>
-          <t>~103786</t>
-        </is>
-      </c>
-      <c r="G23" s="68" t="inlineStr">
-        <is>
-          <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 12 W - FORNECIMENTO E INSTALAÇÃO. AF_09/</t>
-        </is>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I23" s="67" t="inlineStr">
-        <is>
-          <t>44% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="61" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>Spot LED de embutir redondo</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="E25" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F25" s="63" t="n"/>
-      <c r="G25" s="63" t="n"/>
-      <c r="H25" s="63" t="n"/>
-      <c r="I25" s="63" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="64" t="inlineStr"/>
@@ -4204,204 +4206,204 @@
       </c>
       <c r="F26" s="67" t="inlineStr">
         <is>
+          <t>~103786</t>
+        </is>
+      </c>
+      <c r="G26" s="68" t="inlineStr">
+        <is>
+          <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 12 W - FORNECIMENTO E INSTALAÇÃO. AF_09/</t>
+        </is>
+      </c>
+      <c r="H26" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I26" s="67" t="inlineStr">
+        <is>
+          <t>44% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="61" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>Spot LED de embutir redondo</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E28" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="n"/>
+      <c r="G28" s="63" t="n"/>
+      <c r="H28" s="63" t="n"/>
+      <c r="I28" s="63" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="64" t="inlineStr"/>
+      <c r="B29" s="65" t="inlineStr"/>
+      <c r="C29" s="66" t="n"/>
+      <c r="D29" s="66" t="n"/>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F29" s="67" t="inlineStr">
+        <is>
           <t>~105546</t>
         </is>
       </c>
-      <c r="G26" s="68" t="inlineStr">
+      <c r="G29" s="68" t="inlineStr">
         <is>
           <t>LUMINÁRIA TIPO SPOT, DE EMBUTIR, COM 1 LÂMPADA LED PAR20 - FORNECIMENTO E INSTALAÇÃO. AF_09/202</t>
         </is>
       </c>
-      <c r="H26" s="69" t="inlineStr">
+      <c r="H29" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I26" s="67" t="inlineStr">
+      <c r="I29" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="64" t="inlineStr"/>
-      <c r="B27" s="65" t="inlineStr"/>
-      <c r="C27" s="66" t="n"/>
-      <c r="D27" s="66" t="n"/>
-      <c r="E27" s="67" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="64" t="inlineStr"/>
+      <c r="B30" s="65" t="inlineStr"/>
+      <c r="C30" s="66" t="n"/>
+      <c r="D30" s="66" t="n"/>
+      <c r="E30" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F27" s="67" t="inlineStr">
+      <c r="F30" s="67" t="inlineStr">
         <is>
           <t>~105545</t>
         </is>
       </c>
-      <c r="G27" s="68" t="inlineStr">
+      <c r="G30" s="68" t="inlineStr">
         <is>
           <t>LUMINÁRIA TIPO SPOT, DE SOBREPOR, COM 1 LÂMPADA LED PAR20 - FORNECIMENTO E INSTALAÇÃO. AF_09/20</t>
         </is>
       </c>
-      <c r="H27" s="69" t="inlineStr">
+      <c r="H30" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I27" s="67" t="inlineStr">
+      <c r="I30" s="67" t="inlineStr">
         <is>
           <t>28% (texto)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="57" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B29" s="58" t="inlineStr">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t>Pendente decorativo sobre bancada</t>
         </is>
       </c>
-      <c r="C29" s="57" t="inlineStr">
+      <c r="C32" s="57" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D29" s="57" t="n">
+      <c r="D32" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="59" t="inlineStr">
+      <c r="E32" s="59" t="inlineStr">
         <is>
           <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
         </is>
       </c>
-      <c r="F29" s="60" t="n"/>
-      <c r="G29" s="60" t="n"/>
-      <c r="H29" s="60" t="n"/>
-      <c r="I29" s="60" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="F32" s="60" t="n"/>
+      <c r="G32" s="60" t="n"/>
+      <c r="H32" s="60" t="n"/>
+      <c r="I32" s="60" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="61" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B30" s="43" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>Ponto de tomada 2P+T 10A</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D33" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="E30" s="62" t="inlineStr">
+      <c r="E33" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F30" s="63" t="n"/>
-      <c r="G30" s="63" t="n"/>
-      <c r="H30" s="63" t="n"/>
-      <c r="I30" s="63" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="64" t="inlineStr"/>
-      <c r="B31" s="65" t="inlineStr"/>
-      <c r="C31" s="66" t="n"/>
-      <c r="D31" s="66" t="n"/>
-      <c r="E31" s="67" t="inlineStr">
+      <c r="F33" s="63" t="n"/>
+      <c r="G33" s="63" t="n"/>
+      <c r="H33" s="63" t="n"/>
+      <c r="I33" s="63" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="inlineStr"/>
+      <c r="B34" s="65" t="inlineStr"/>
+      <c r="C34" s="66" t="n"/>
+      <c r="D34" s="66" t="n"/>
+      <c r="E34" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F31" s="67" t="inlineStr">
-        <is>
-          <t>~92004</t>
-        </is>
-      </c>
-      <c r="G31" s="68" t="inlineStr">
-        <is>
-          <t>TOMADA MÉDIA DE EMBUTIR (2 MÓDULOS), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INST</t>
-        </is>
-      </c>
-      <c r="H31" s="69" t="inlineStr">
+      <c r="F34" s="67" t="inlineStr">
+        <is>
+          <t>91996</t>
+        </is>
+      </c>
+      <c r="G34" s="68" t="inlineStr">
+        <is>
+          <t>TOMADA MÉDIA DE EMBUTIR (1 MÓDULO), 2P+T 10 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTA</t>
+        </is>
+      </c>
+      <c r="H34" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I31" s="67" t="inlineStr">
+      <c r="I34" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="64" t="inlineStr"/>
-      <c r="B32" s="65" t="inlineStr"/>
-      <c r="C32" s="66" t="n"/>
-      <c r="D32" s="66" t="n"/>
-      <c r="E32" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F32" s="67" t="inlineStr">
-        <is>
-          <t>~91997</t>
-        </is>
-      </c>
-      <c r="G32" s="68" t="inlineStr">
-        <is>
-          <t>TOMADA MÉDIA DE EMBUTIR (1 MÓDULO), 2P+T 20 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTA</t>
-        </is>
-      </c>
-      <c r="H32" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I32" s="67" t="inlineStr">
-        <is>
-          <t>33% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="61" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>Ponto de interruptor</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="E34" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F34" s="63" t="n"/>
-      <c r="G34" s="63" t="n"/>
-      <c r="H34" s="63" t="n"/>
-      <c r="I34" s="63" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="64" t="inlineStr"/>
@@ -4415,12 +4417,12 @@
       </c>
       <c r="F35" s="67" t="inlineStr">
         <is>
-          <t>~91953</t>
+          <t>~91997</t>
         </is>
       </c>
       <c r="G35" s="68" t="inlineStr">
         <is>
-          <t>INTERRUPTOR SIMPLES (1 MÓDULO), 10A/250V, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTALAÇÃO</t>
+          <t>TOMADA MÉDIA DE EMBUTIR (1 MÓDULO), 2P+T 20 A, INCLUINDO SUPORTE E PLACA - FORNECIMENTO E INSTA</t>
         </is>
       </c>
       <c r="H35" s="69" t="inlineStr">
@@ -4430,69 +4432,69 @@
       </c>
       <c r="I35" s="67" t="inlineStr">
         <is>
+          <t>33% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="61" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Ponto de interruptor</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E37" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F37" s="63" t="n"/>
+      <c r="G37" s="63" t="n"/>
+      <c r="H37" s="63" t="n"/>
+      <c r="I37" s="63" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr"/>
+      <c r="B38" s="65" t="inlineStr"/>
+      <c r="C38" s="66" t="n"/>
+      <c r="D38" s="66" t="n"/>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F38" s="67" t="inlineStr">
+        <is>
+          <t>~91952</t>
+        </is>
+      </c>
+      <c r="G38" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERRUPTOR SIMPLES (1 MÓDULO), 10A/250V, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇÃO. </t>
+        </is>
+      </c>
+      <c r="H38" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I38" s="67" t="inlineStr">
+        <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="64" t="inlineStr"/>
-      <c r="B36" s="65" t="inlineStr"/>
-      <c r="C36" s="66" t="n"/>
-      <c r="D36" s="66" t="n"/>
-      <c r="E36" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F36" s="67" t="inlineStr">
-        <is>
-          <t>~91954</t>
-        </is>
-      </c>
-      <c r="G36" s="68" t="inlineStr">
-        <is>
-          <t>INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇÃO.</t>
-        </is>
-      </c>
-      <c r="H36" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I36" s="67" t="inlineStr">
-        <is>
-          <t>61% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="61" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
-        <is>
-          <t>Ponto de rede/dados RJ45 cat6</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="E38" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F38" s="63" t="n"/>
-      <c r="G38" s="63" t="n"/>
-      <c r="H38" s="63" t="n"/>
-      <c r="I38" s="63" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="64" t="inlineStr"/>
@@ -4506,84 +4508,84 @@
       </c>
       <c r="F39" s="67" t="inlineStr">
         <is>
+          <t>~91954</t>
+        </is>
+      </c>
+      <c r="G39" s="68" t="inlineStr">
+        <is>
+          <t>INTERRUPTOR PARALELO (1 MÓDULO), 10A/250V, SEM SUPORTE E SEM PLACA - FORNECIMENTO E INSTALAÇÃO.</t>
+        </is>
+      </c>
+      <c r="H39" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I39" s="67" t="inlineStr">
+        <is>
+          <t>61% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Ponto de rede/dados RJ45 cat6</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F41" s="63" t="n"/>
+      <c r="G41" s="63" t="n"/>
+      <c r="H41" s="63" t="n"/>
+      <c r="I41" s="63" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr"/>
+      <c r="B42" s="65" t="inlineStr"/>
+      <c r="C42" s="66" t="n"/>
+      <c r="D42" s="66" t="n"/>
+      <c r="E42" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F42" s="67" t="inlineStr">
+        <is>
           <t>106077</t>
         </is>
       </c>
-      <c r="G39" s="68" t="inlineStr">
+      <c r="G42" s="68" t="inlineStr">
         <is>
           <t>TOMADA RJ45 CAT 6E (COMPLETA) - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
         </is>
       </c>
-      <c r="H39" s="69" t="inlineStr">
+      <c r="H42" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I39" s="67" t="inlineStr">
+      <c r="I42" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="64" t="inlineStr"/>
-      <c r="B40" s="65" t="inlineStr"/>
-      <c r="C40" s="66" t="n"/>
-      <c r="D40" s="66" t="n"/>
-      <c r="E40" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F40" s="67" t="inlineStr">
-        <is>
-          <t>98307</t>
-        </is>
-      </c>
-      <c r="G40" s="68" t="inlineStr">
-        <is>
-          <t>TOMADA DE REDE RJ45 - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
-        </is>
-      </c>
-      <c r="H40" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I40" s="67" t="inlineStr">
-        <is>
-          <t>40% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="61" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
-        <is>
-          <t>Bacia sanitária com caixa acoplada</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F42" s="63" t="n"/>
-      <c r="G42" s="63" t="n"/>
-      <c r="H42" s="63" t="n"/>
-      <c r="I42" s="63" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="64" t="inlineStr"/>
@@ -4597,204 +4599,204 @@
       </c>
       <c r="F43" s="67" t="inlineStr">
         <is>
+          <t>98307</t>
+        </is>
+      </c>
+      <c r="G43" s="68" t="inlineStr">
+        <is>
+          <t>TOMADA DE REDE RJ45 - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+        </is>
+      </c>
+      <c r="H43" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I43" s="67" t="inlineStr">
+        <is>
+          <t>40% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="61" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="inlineStr">
+        <is>
+          <t>Bacia sanitária com caixa acoplada</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F45" s="63" t="n"/>
+      <c r="G45" s="63" t="n"/>
+      <c r="H45" s="63" t="n"/>
+      <c r="I45" s="63" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="64" t="inlineStr"/>
+      <c r="B46" s="65" t="inlineStr"/>
+      <c r="C46" s="66" t="n"/>
+      <c r="D46" s="66" t="n"/>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F46" s="67" t="inlineStr">
+        <is>
           <t>86888</t>
         </is>
       </c>
-      <c r="G43" s="68" t="inlineStr">
+      <c r="G46" s="68" t="inlineStr">
         <is>
           <t>BACIA SANITÁRIA COM CAIXA ACOPLADA LOUÇA BRANCA - FORNECIMENTO E INSTALAÇÃO. AF_02/2026</t>
         </is>
       </c>
-      <c r="H43" s="69" t="inlineStr">
+      <c r="H46" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I43" s="67" t="inlineStr">
+      <c r="I46" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="64" t="inlineStr"/>
-      <c r="B44" s="65" t="inlineStr"/>
-      <c r="C44" s="66" t="n"/>
-      <c r="D44" s="66" t="n"/>
-      <c r="E44" s="67" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="64" t="inlineStr"/>
+      <c r="B47" s="65" t="inlineStr"/>
+      <c r="C47" s="66" t="n"/>
+      <c r="D47" s="66" t="n"/>
+      <c r="E47" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F44" s="67" t="inlineStr">
+      <c r="F47" s="67" t="inlineStr">
         <is>
           <t>~100848</t>
         </is>
       </c>
-      <c r="G44" s="68" t="inlineStr">
+      <c r="G47" s="68" t="inlineStr">
         <is>
           <t>BACIA SANITÁRIA INFANTIL LOUÇA BRANCA, COM TUBO DE LIGAÇÃO CROMADO - FORNECIMENTO E INSTALAÇÃO.</t>
         </is>
       </c>
-      <c r="H44" s="69" t="inlineStr">
+      <c r="H47" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I44" s="67" t="inlineStr">
+      <c r="I47" s="67" t="inlineStr">
         <is>
           <t>45% (texto)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="57" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B46" s="58" t="inlineStr">
+      <c r="B49" s="58" t="inlineStr">
         <is>
           <t>Cuba de apoio + torneira (copa)</t>
         </is>
       </c>
-      <c r="C46" s="57" t="inlineStr">
+      <c r="C49" s="57" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D46" s="57" t="n">
+      <c r="D49" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="59" t="inlineStr">
+      <c r="E49" s="59" t="inlineStr">
         <is>
           <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
         </is>
       </c>
-      <c r="F46" s="60" t="n"/>
-      <c r="G46" s="60" t="n"/>
-      <c r="H46" s="60" t="n"/>
-      <c r="I46" s="60" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="61" t="inlineStr">
+      <c r="F49" s="60" t="n"/>
+      <c r="G49" s="60" t="n"/>
+      <c r="H49" s="60" t="n"/>
+      <c r="I49" s="60" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="61" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>Ar-condicionado split cassete 36.000 BTU</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D47" s="23" t="n">
+      <c r="D50" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="62" t="inlineStr">
+      <c r="E50" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F47" s="63" t="n"/>
-      <c r="G47" s="63" t="n"/>
-      <c r="H47" s="63" t="n"/>
-      <c r="I47" s="63" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="64" t="inlineStr"/>
-      <c r="B48" s="65" t="inlineStr"/>
-      <c r="C48" s="66" t="n"/>
-      <c r="D48" s="66" t="n"/>
-      <c r="E48" s="67" t="inlineStr">
+      <c r="F50" s="63" t="n"/>
+      <c r="G50" s="63" t="n"/>
+      <c r="H50" s="63" t="n"/>
+      <c r="I50" s="63" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="64" t="inlineStr"/>
+      <c r="B51" s="65" t="inlineStr"/>
+      <c r="C51" s="66" t="n"/>
+      <c r="D51" s="66" t="n"/>
+      <c r="E51" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F48" s="67" t="inlineStr">
+      <c r="F51" s="67" t="inlineStr">
         <is>
           <t>103271</t>
         </is>
       </c>
-      <c r="G48" s="68" t="inlineStr">
+      <c r="G51" s="68" t="inlineStr">
         <is>
           <t>AR CONDICIONADO SPLIT ON/OFF, CASSETE (TETO), FRIO 4 VIAS 36000 BTU/H - FORNECIMENTO E INSTALAÇ</t>
         </is>
       </c>
-      <c r="H48" s="69" t="inlineStr">
+      <c r="H51" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I48" s="67" t="inlineStr">
+      <c r="I51" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="64" t="inlineStr"/>
-      <c r="B49" s="65" t="inlineStr"/>
-      <c r="C49" s="66" t="n"/>
-      <c r="D49" s="66" t="n"/>
-      <c r="E49" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F49" s="67" t="inlineStr">
-        <is>
-          <t>~89866</t>
-        </is>
-      </c>
-      <c r="G49" s="68" t="inlineStr">
-        <is>
-          <t>JOELHO 90 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM DRENO DE AR-CONDICIONADO - FORNECIMENTO E</t>
-        </is>
-      </c>
-      <c r="H49" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I49" s="67" t="inlineStr">
-        <is>
-          <t>40% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="61" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B51" s="43" t="inlineStr">
-        <is>
-          <t>Alvenaria de bloco cerâmico e=14cm</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="E51" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F51" s="63" t="n"/>
-      <c r="G51" s="63" t="n"/>
-      <c r="H51" s="63" t="n"/>
-      <c r="I51" s="63" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="64" t="inlineStr"/>
@@ -4808,84 +4810,84 @@
       </c>
       <c r="F52" s="67" t="inlineStr">
         <is>
+          <t>~89866</t>
+        </is>
+      </c>
+      <c r="G52" s="68" t="inlineStr">
+        <is>
+          <t>JOELHO 90 GRAUS, PVC, SOLDÁVEL, DN 25MM, INSTALADO EM DRENO DE AR-CONDICIONADO - FORNECIMENTO E</t>
+        </is>
+      </c>
+      <c r="H52" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I52" s="67" t="inlineStr">
+        <is>
+          <t>40% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B54" s="43" t="inlineStr">
+        <is>
+          <t>Alvenaria de bloco cerâmico e=14cm</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E54" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F54" s="63" t="n"/>
+      <c r="G54" s="63" t="n"/>
+      <c r="H54" s="63" t="n"/>
+      <c r="I54" s="63" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="64" t="inlineStr"/>
+      <c r="B55" s="65" t="inlineStr"/>
+      <c r="C55" s="66" t="n"/>
+      <c r="D55" s="66" t="n"/>
+      <c r="E55" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F55" s="67" t="inlineStr">
+        <is>
           <t>89290</t>
         </is>
       </c>
-      <c r="G52" s="68" t="inlineStr">
+      <c r="G55" s="68" t="inlineStr">
         <is>
           <t>ALVENARIA ESTRUTURAL DE BLOCOS CERÂMICOS 14X19X29, (ESPESSURA DE 14 CM), UTILIZANDO PALHETA E A</t>
         </is>
       </c>
-      <c r="H52" s="69" t="inlineStr">
+      <c r="H55" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I52" s="67" t="inlineStr">
+      <c r="I55" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="64" t="inlineStr"/>
-      <c r="B53" s="65" t="inlineStr"/>
-      <c r="C53" s="66" t="n"/>
-      <c r="D53" s="66" t="n"/>
-      <c r="E53" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F53" s="67" t="inlineStr">
-        <is>
-          <t>~104441</t>
-        </is>
-      </c>
-      <c r="G53" s="68" t="inlineStr">
-        <is>
-          <t>ALVENARIA DE BLOCOS DE CONCRETO ESTRUTURAL 14X19X39 CM (ESPESSURA 14 CM), FBK = 8 MPA, UTILIZAN</t>
-        </is>
-      </c>
-      <c r="H53" s="69" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I53" s="67" t="inlineStr">
-        <is>
-          <t>52% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="61" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B55" s="43" t="inlineStr">
-        <is>
-          <t>Divisória em drywall (2 faces, com lã)</t>
-        </is>
-      </c>
-      <c r="C55" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D55" s="23" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E55" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F55" s="63" t="n"/>
-      <c r="G55" s="63" t="n"/>
-      <c r="H55" s="63" t="n"/>
-      <c r="I55" s="63" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="64" t="inlineStr"/>
@@ -4899,84 +4901,84 @@
       </c>
       <c r="F56" s="67" t="inlineStr">
         <is>
+          <t>~104441</t>
+        </is>
+      </c>
+      <c r="G56" s="68" t="inlineStr">
+        <is>
+          <t>ALVENARIA DE BLOCOS DE CONCRETO ESTRUTURAL 14X19X39 CM (ESPESSURA 14 CM), FBK = 8 MPA, UTILIZAN</t>
+        </is>
+      </c>
+      <c r="H56" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I56" s="67" t="inlineStr">
+        <is>
+          <t>52% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="61" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B58" s="43" t="inlineStr">
+        <is>
+          <t>Divisória em drywall (2 faces, com lã)</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E58" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F58" s="63" t="n"/>
+      <c r="G58" s="63" t="n"/>
+      <c r="H58" s="63" t="n"/>
+      <c r="I58" s="63" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="64" t="inlineStr"/>
+      <c r="B59" s="65" t="inlineStr"/>
+      <c r="C59" s="66" t="n"/>
+      <c r="D59" s="66" t="n"/>
+      <c r="E59" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F59" s="67" t="inlineStr">
+        <is>
           <t>96361</t>
         </is>
       </c>
-      <c r="G56" s="68" t="inlineStr">
+      <c r="G59" s="68" t="inlineStr">
         <is>
           <t>PAREDE COM SISTEMA EM CHAPAS DE GESSO PARA DRYWALL, USO INTERNO, COM DUAS FACES SIMPLES E ESTRU</t>
         </is>
       </c>
-      <c r="H56" s="69" t="inlineStr">
+      <c r="H59" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I56" s="67" t="inlineStr">
+      <c r="I59" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="64" t="inlineStr"/>
-      <c r="B57" s="65" t="inlineStr"/>
-      <c r="C57" s="66" t="n"/>
-      <c r="D57" s="66" t="n"/>
-      <c r="E57" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F57" s="67" t="inlineStr">
-        <is>
-          <t>~102450</t>
-        </is>
-      </c>
-      <c r="G57" s="68" t="inlineStr">
-        <is>
-          <t>DIVISORIA (N2) - PAINEL/VIDRO - PAINEL C/ MSO/COMEIA E=35MM - PERFIS SIMPLES ACO GALVANIZADO PI</t>
-        </is>
-      </c>
-      <c r="H57" s="69" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I57" s="67" t="inlineStr">
-        <is>
-          <t>28% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="61" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B59" s="43" t="inlineStr">
-        <is>
-          <t>Contrapiso desempenado e=4cm</t>
-        </is>
-      </c>
-      <c r="C59" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D59" s="23" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E59" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F59" s="63" t="n"/>
-      <c r="G59" s="63" t="n"/>
-      <c r="H59" s="63" t="n"/>
-      <c r="I59" s="63" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="64" t="inlineStr"/>
@@ -4990,84 +4992,84 @@
       </c>
       <c r="F60" s="67" t="inlineStr">
         <is>
+          <t>~102450</t>
+        </is>
+      </c>
+      <c r="G60" s="68" t="inlineStr">
+        <is>
+          <t>DIVISORIA (N2) - PAINEL/VIDRO - PAINEL C/ MSO/COMEIA E=35MM - PERFIS SIMPLES ACO GALVANIZADO PI</t>
+        </is>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I60" s="67" t="inlineStr">
+        <is>
+          <t>28% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="61" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B62" s="43" t="inlineStr">
+        <is>
+          <t>Contrapiso desempenado e=4cm</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="E62" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F62" s="63" t="n"/>
+      <c r="G62" s="63" t="n"/>
+      <c r="H62" s="63" t="n"/>
+      <c r="I62" s="63" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="64" t="inlineStr"/>
+      <c r="B63" s="65" t="inlineStr"/>
+      <c r="C63" s="66" t="n"/>
+      <c r="D63" s="66" t="n"/>
+      <c r="E63" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F63" s="67" t="inlineStr">
+        <is>
           <t>~88478</t>
         </is>
       </c>
-      <c r="G60" s="68" t="inlineStr">
+      <c r="G63" s="68" t="inlineStr">
         <is>
           <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 4CM. AF_07/2021</t>
         </is>
       </c>
-      <c r="H60" s="69" t="inlineStr">
+      <c r="H63" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I60" s="67" t="inlineStr">
+      <c r="I63" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="64" t="inlineStr"/>
-      <c r="B61" s="65" t="inlineStr"/>
-      <c r="C61" s="66" t="n"/>
-      <c r="D61" s="66" t="n"/>
-      <c r="E61" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F61" s="67" t="inlineStr">
-        <is>
-          <t>~88476</t>
-        </is>
-      </c>
-      <c r="G61" s="68" t="inlineStr">
-        <is>
-          <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 2CM. AF_07/2021</t>
-        </is>
-      </c>
-      <c r="H61" s="69" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I61" s="67" t="inlineStr">
-        <is>
-          <t>37% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="61" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B63" s="43" t="inlineStr">
-        <is>
-          <t>Piso porcelanato retificado 60x60</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D63" s="23" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="E63" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F63" s="63" t="n"/>
-      <c r="G63" s="63" t="n"/>
-      <c r="H63" s="63" t="n"/>
-      <c r="I63" s="63" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="64" t="inlineStr"/>
@@ -5081,84 +5083,84 @@
       </c>
       <c r="F64" s="67" t="inlineStr">
         <is>
+          <t>~88476</t>
+        </is>
+      </c>
+      <c r="G64" s="68" t="inlineStr">
+        <is>
+          <t>CONTRAPISO COM ARGAMASSA AUTONIVELANTE, APLICADO SOBRE LAJE, ADERIDO, ESPESSURA 2CM. AF_07/2021</t>
+        </is>
+      </c>
+      <c r="H64" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I64" s="67" t="inlineStr">
+        <is>
+          <t>37% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="61" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B66" s="43" t="inlineStr">
+        <is>
+          <t>Piso porcelanato retificado 60x60</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E66" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F66" s="63" t="n"/>
+      <c r="G66" s="63" t="n"/>
+      <c r="H66" s="63" t="n"/>
+      <c r="I66" s="63" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="64" t="inlineStr"/>
+      <c r="B67" s="65" t="inlineStr"/>
+      <c r="C67" s="66" t="n"/>
+      <c r="D67" s="66" t="n"/>
+      <c r="E67" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F67" s="67" t="inlineStr">
+        <is>
           <t>87261</t>
         </is>
       </c>
-      <c r="G64" s="68" t="inlineStr">
+      <c r="G67" s="68" t="inlineStr">
         <is>
           <t>REVESTIMENTO CERÂMICO PARA PISO COM PLACAS TIPO PORCELANATO DE DIMENSÕES 60X60 CM APLICADA EM A</t>
         </is>
       </c>
-      <c r="H64" s="69" t="inlineStr">
+      <c r="H67" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I64" s="67" t="inlineStr">
+      <c r="I67" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="64" t="inlineStr"/>
-      <c r="B65" s="65" t="inlineStr"/>
-      <c r="C65" s="66" t="n"/>
-      <c r="D65" s="66" t="n"/>
-      <c r="E65" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F65" s="67" t="inlineStr">
-        <is>
-          <t>~101735</t>
-        </is>
-      </c>
-      <c r="G65" s="68" t="inlineStr">
-        <is>
-          <t>PISO DE BORRACHA ESPORTIVO, ESPESSURA 15MM, ASSENTADO COM ARGAMASSA. AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H65" s="69" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I65" s="67" t="inlineStr">
-        <is>
-          <t>15% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="61" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B67" s="43" t="inlineStr">
-        <is>
-          <t>Rodapé em porcelanato h=7cm</t>
-        </is>
-      </c>
-      <c r="C67" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D67" s="23" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="E67" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F67" s="63" t="n"/>
-      <c r="G67" s="63" t="n"/>
-      <c r="H67" s="63" t="n"/>
-      <c r="I67" s="63" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="64" t="inlineStr"/>
@@ -5172,84 +5174,84 @@
       </c>
       <c r="F68" s="67" t="inlineStr">
         <is>
+          <t>~101735</t>
+        </is>
+      </c>
+      <c r="G68" s="68" t="inlineStr">
+        <is>
+          <t>PISO DE BORRACHA ESPORTIVO, ESPESSURA 15MM, ASSENTADO COM ARGAMASSA. AF_02/2026</t>
+        </is>
+      </c>
+      <c r="H68" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I68" s="67" t="inlineStr">
+        <is>
+          <t>15% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="61" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
+        <is>
+          <t>Rodapé em porcelanato h=7cm</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="E70" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F70" s="63" t="n"/>
+      <c r="G70" s="63" t="n"/>
+      <c r="H70" s="63" t="n"/>
+      <c r="I70" s="63" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="64" t="inlineStr"/>
+      <c r="B71" s="65" t="inlineStr"/>
+      <c r="C71" s="66" t="n"/>
+      <c r="D71" s="66" t="n"/>
+      <c r="E71" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F71" s="67" t="inlineStr">
+        <is>
           <t>~88650</t>
         </is>
       </c>
-      <c r="G68" s="68" t="inlineStr">
+      <c r="G71" s="68" t="inlineStr">
         <is>
           <t>RODAPÉ CERÂMICO DE 7CM DE ALTURA COM PLACAS TIPO ESMALTADA DE DIMENSÕES 60X60CM. AF_02/2023</t>
         </is>
       </c>
-      <c r="H68" s="69" t="inlineStr">
+      <c r="H71" s="69" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I68" s="67" t="inlineStr">
+      <c r="I71" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="64" t="inlineStr"/>
-      <c r="B69" s="65" t="inlineStr"/>
-      <c r="C69" s="66" t="n"/>
-      <c r="D69" s="66" t="n"/>
-      <c r="E69" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F69" s="67" t="inlineStr">
-        <is>
-          <t>~104619</t>
-        </is>
-      </c>
-      <c r="G69" s="68" t="inlineStr">
-        <is>
-          <t>RODAPÉ CERÂMICO DE 7CM DE ALTURA COM PLACAS TIPO ESMALTADA DE DIMENSÕES 80X80CM. AF_02/2023</t>
-        </is>
-      </c>
-      <c r="H69" s="69" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I69" s="67" t="inlineStr">
-        <is>
-          <t>27% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="61" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B71" s="43" t="inlineStr">
-        <is>
-          <t>Piso vinílico em manta (sala de reunião)</t>
-        </is>
-      </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D71" s="23" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E71" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F71" s="63" t="n"/>
-      <c r="G71" s="63" t="n"/>
-      <c r="H71" s="63" t="n"/>
-      <c r="I71" s="63" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="64" t="inlineStr"/>
@@ -5263,84 +5265,84 @@
       </c>
       <c r="F72" s="67" t="inlineStr">
         <is>
+          <t>~104619</t>
+        </is>
+      </c>
+      <c r="G72" s="68" t="inlineStr">
+        <is>
+          <t>RODAPÉ CERÂMICO DE 7CM DE ALTURA COM PLACAS TIPO ESMALTADA DE DIMENSÕES 80X80CM. AF_02/2023</t>
+        </is>
+      </c>
+      <c r="H72" s="69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I72" s="67" t="inlineStr">
+        <is>
+          <t>27% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="61" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B74" s="43" t="inlineStr">
+        <is>
+          <t>Piso vinílico em manta (sala de reunião)</t>
+        </is>
+      </c>
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E74" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F74" s="63" t="n"/>
+      <c r="G74" s="63" t="n"/>
+      <c r="H74" s="63" t="n"/>
+      <c r="I74" s="63" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="64" t="inlineStr"/>
+      <c r="B75" s="65" t="inlineStr"/>
+      <c r="C75" s="66" t="n"/>
+      <c r="D75" s="66" t="n"/>
+      <c r="E75" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F75" s="67" t="inlineStr">
+        <is>
           <t>101728</t>
         </is>
       </c>
-      <c r="G72" s="68" t="inlineStr">
+      <c r="G75" s="68" t="inlineStr">
         <is>
           <t>PISO VINÍLICO FLEXÍVEL EM MANTA, PADRÃO LISO, ESPESSURA 2 MM, FIXADO COM COLA. AF_02/2026</t>
         </is>
       </c>
-      <c r="H72" s="69" t="inlineStr">
+      <c r="H75" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I72" s="67" t="inlineStr">
+      <c r="I75" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="64" t="inlineStr"/>
-      <c r="B73" s="65" t="inlineStr"/>
-      <c r="C73" s="66" t="n"/>
-      <c r="D73" s="66" t="n"/>
-      <c r="E73" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F73" s="67" t="inlineStr">
-        <is>
-          <t>~101735</t>
-        </is>
-      </c>
-      <c r="G73" s="68" t="inlineStr">
-        <is>
-          <t>PISO DE BORRACHA ESPORTIVO, ESPESSURA 15MM, ASSENTADO COM ARGAMASSA. AF_02/2026</t>
-        </is>
-      </c>
-      <c r="H73" s="69" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="I73" s="67" t="inlineStr">
-        <is>
-          <t>20% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="61" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B75" s="43" t="inlineStr">
-        <is>
-          <t>Pintura látex acrílica em parede (2 demãos)</t>
-        </is>
-      </c>
-      <c r="C75" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D75" s="23" t="n">
-        <v>214</v>
-      </c>
-      <c r="E75" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F75" s="63" t="n"/>
-      <c r="G75" s="63" t="n"/>
-      <c r="H75" s="63" t="n"/>
-      <c r="I75" s="63" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="64" t="inlineStr"/>
@@ -5354,204 +5356,204 @@
       </c>
       <c r="F76" s="67" t="inlineStr">
         <is>
+          <t>~101735</t>
+        </is>
+      </c>
+      <c r="G76" s="68" t="inlineStr">
+        <is>
+          <t>PISO DE BORRACHA ESPORTIVO, ESPESSURA 15MM, ASSENTADO COM ARGAMASSA. AF_02/2026</t>
+        </is>
+      </c>
+      <c r="H76" s="69" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="I76" s="67" t="inlineStr">
+        <is>
+          <t>20% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="61" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>Pintura látex acrílica em parede (2 demãos)</t>
+        </is>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="n">
+        <v>214</v>
+      </c>
+      <c r="E78" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F78" s="63" t="n"/>
+      <c r="G78" s="63" t="n"/>
+      <c r="H78" s="63" t="n"/>
+      <c r="I78" s="63" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="64" t="inlineStr"/>
+      <c r="B79" s="65" t="inlineStr"/>
+      <c r="C79" s="66" t="n"/>
+      <c r="D79" s="66" t="n"/>
+      <c r="E79" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F79" s="67" t="inlineStr">
+        <is>
           <t>~88489</t>
         </is>
       </c>
-      <c r="G76" s="68" t="inlineStr">
+      <c r="G79" s="68" t="inlineStr">
         <is>
           <t>PINTURA LÁTEX ACRÍLICA PREMIUM, APLICAÇÃO MANUAL EM PAREDES, DUAS DEMÃOS. AF_04/2023</t>
         </is>
       </c>
-      <c r="H76" s="69" t="inlineStr">
+      <c r="H79" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I76" s="67" t="inlineStr">
+      <c r="I79" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="64" t="inlineStr"/>
-      <c r="B77" s="65" t="inlineStr"/>
-      <c r="C77" s="66" t="n"/>
-      <c r="D77" s="66" t="n"/>
-      <c r="E77" s="67" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="64" t="inlineStr"/>
+      <c r="B80" s="65" t="inlineStr"/>
+      <c r="C80" s="66" t="n"/>
+      <c r="D80" s="66" t="n"/>
+      <c r="E80" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F77" s="67" t="inlineStr">
+      <c r="F80" s="67" t="inlineStr">
         <is>
           <t>~102491</t>
         </is>
       </c>
-      <c r="G77" s="68" t="inlineStr">
+      <c r="G80" s="68" t="inlineStr">
         <is>
           <t>PINTURA DE PISO COM TINTA ACRÍLICA, APLICAÇÃO MANUAL, 2 DEMÃOS, INCLUSO FUNDO PREPARADOR. AF_05</t>
         </is>
       </c>
-      <c r="H77" s="69" t="inlineStr">
+      <c r="H80" s="69" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I77" s="67" t="inlineStr">
+      <c r="I80" s="67" t="inlineStr">
         <is>
           <t>40% (texto)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="57" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="57" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="B79" s="58" t="inlineStr">
+      <c r="B82" s="58" t="inlineStr">
         <is>
           <t>Pintura em forro de gesso</t>
         </is>
       </c>
-      <c r="C79" s="57" t="inlineStr">
+      <c r="C82" s="57" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D79" s="57" t="n">
+      <c r="D82" s="57" t="n">
         <v>101.7</v>
       </c>
-      <c r="E79" s="59" t="inlineStr">
+      <c r="E82" s="59" t="inlineStr">
         <is>
           <t>Sem correspondência no SINAPI — a IA conferiu os candidatos e nenhum é o mesmo serviço. Buscar manualmente em https://www.caixa.gov.br/sinapi</t>
         </is>
       </c>
-      <c r="F79" s="60" t="n"/>
-      <c r="G79" s="60" t="n"/>
-      <c r="H79" s="60" t="n"/>
-      <c r="I79" s="60" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="61" t="inlineStr">
+      <c r="F82" s="60" t="n"/>
+      <c r="G82" s="60" t="n"/>
+      <c r="H82" s="60" t="n"/>
+      <c r="I82" s="60" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="61" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="B80" s="43" t="inlineStr">
+      <c r="B83" s="43" t="inlineStr">
         <is>
           <t>Porta de madeira 80x210 com batente e ferragens</t>
         </is>
       </c>
-      <c r="C80" s="23" t="inlineStr">
+      <c r="C83" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D80" s="23" t="n">
+      <c r="D83" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E80" s="62" t="inlineStr">
+      <c r="E83" s="62" t="inlineStr">
         <is>
           <t>↓ matches encontrados ↓</t>
         </is>
       </c>
-      <c r="F80" s="63" t="n"/>
-      <c r="G80" s="63" t="n"/>
-      <c r="H80" s="63" t="n"/>
-      <c r="I80" s="63" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="64" t="inlineStr"/>
-      <c r="B81" s="65" t="inlineStr"/>
-      <c r="C81" s="66" t="n"/>
-      <c r="D81" s="66" t="n"/>
-      <c r="E81" s="67" t="inlineStr">
+      <c r="F83" s="63" t="n"/>
+      <c r="G83" s="63" t="n"/>
+      <c r="H83" s="63" t="n"/>
+      <c r="I83" s="63" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="64" t="inlineStr"/>
+      <c r="B84" s="65" t="inlineStr"/>
+      <c r="C84" s="66" t="n"/>
+      <c r="D84" s="66" t="n"/>
+      <c r="E84" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F81" s="67" t="inlineStr">
+      <c r="F84" s="67" t="inlineStr">
         <is>
           <t>91297</t>
         </is>
       </c>
-      <c r="G81" s="68" t="inlineStr">
+      <c r="G84" s="68" t="inlineStr">
         <is>
           <t>PORTA DE MADEIRA FRISADA, SEMI-OCA (LEVE OU MÉDIA), 80X210CM, ESPESSURA DE 3,5CM, INCLUSO DOBRA</t>
         </is>
       </c>
-      <c r="H81" s="69" t="inlineStr">
+      <c r="H84" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I81" s="67" t="inlineStr">
+      <c r="I84" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="64" t="inlineStr"/>
-      <c r="B82" s="65" t="inlineStr"/>
-      <c r="C82" s="66" t="n"/>
-      <c r="D82" s="66" t="n"/>
-      <c r="E82" s="67" t="inlineStr">
-        <is>
-          <t>SINAPI</t>
-        </is>
-      </c>
-      <c r="F82" s="67" t="inlineStr">
-        <is>
-          <t>~106319</t>
-        </is>
-      </c>
-      <c r="G82" s="68" t="inlineStr">
-        <is>
-          <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 80X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
-        </is>
-      </c>
-      <c r="H82" s="69" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="I82" s="67" t="inlineStr">
-        <is>
-          <t>25% (texto)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="61" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B84" s="43" t="inlineStr">
-        <is>
-          <t>Porta de vidro temperado 90x210</t>
-        </is>
-      </c>
-      <c r="C84" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D84" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" s="62" t="inlineStr">
-        <is>
-          <t>↓ matches encontrados ↓</t>
-        </is>
-      </c>
-      <c r="F84" s="63" t="n"/>
-      <c r="G84" s="63" t="n"/>
-      <c r="H84" s="63" t="n"/>
-      <c r="I84" s="63" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="64" t="inlineStr"/>
@@ -5565,58 +5567,118 @@
       </c>
       <c r="F85" s="67" t="inlineStr">
         <is>
+          <t>~106319</t>
+        </is>
+      </c>
+      <c r="G85" s="68" t="inlineStr">
+        <is>
+          <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 80X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
+        </is>
+      </c>
+      <c r="H85" s="69" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="I85" s="67" t="inlineStr">
+        <is>
+          <t>25% (texto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="61" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="B87" s="43" t="inlineStr">
+        <is>
+          <t>Porta de vidro temperado 90x210</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="62" t="inlineStr">
+        <is>
+          <t>↓ matches encontrados ↓</t>
+        </is>
+      </c>
+      <c r="F87" s="63" t="n"/>
+      <c r="G87" s="63" t="n"/>
+      <c r="H87" s="63" t="n"/>
+      <c r="I87" s="63" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="64" t="inlineStr"/>
+      <c r="B88" s="65" t="inlineStr"/>
+      <c r="C88" s="66" t="n"/>
+      <c r="D88" s="66" t="n"/>
+      <c r="E88" s="67" t="inlineStr">
+        <is>
+          <t>SINAPI</t>
+        </is>
+      </c>
+      <c r="F88" s="67" t="inlineStr">
+        <is>
           <t>102184</t>
         </is>
       </c>
-      <c r="G85" s="68" t="inlineStr">
+      <c r="G88" s="68" t="inlineStr">
         <is>
           <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 90X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
         </is>
       </c>
-      <c r="H85" s="69" t="inlineStr">
+      <c r="H88" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I85" s="67" t="inlineStr">
+      <c r="I88" s="67" t="inlineStr">
         <is>
           <t>✓ IA conferiu</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="64" t="inlineStr"/>
-      <c r="B86" s="65" t="inlineStr"/>
-      <c r="C86" s="66" t="n"/>
-      <c r="D86" s="66" t="n"/>
-      <c r="E86" s="67" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="64" t="inlineStr"/>
+      <c r="B89" s="65" t="inlineStr"/>
+      <c r="C89" s="66" t="n"/>
+      <c r="D89" s="66" t="n"/>
+      <c r="E89" s="67" t="inlineStr">
         <is>
           <t>SINAPI</t>
         </is>
       </c>
-      <c r="F86" s="67" t="inlineStr">
+      <c r="F89" s="67" t="inlineStr">
         <is>
           <t>~106319</t>
         </is>
       </c>
-      <c r="G86" s="68" t="inlineStr">
+      <c r="G89" s="68" t="inlineStr">
         <is>
           <t>PORTA DE ABRIR COM MOLA HIDRÁULICA, EM VIDRO TEMPERADO, 80X210 CM, ESPESSURA 10 MM, INCLUSIVE A</t>
         </is>
       </c>
-      <c r="H86" s="69" t="inlineStr">
+      <c r="H89" s="69" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I86" s="67" t="inlineStr">
+      <c r="I89" s="67" t="inlineStr">
         <is>
           <t>57% (texto)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>Como ler: MATCH % indica a similaridade entre a descrição do item e a composição SINAPI. Acima de 70% = referência forte. 40-70% = revisar. Abaixo de 30% = candidato fraco, buscar código manualmente em https://www.caixa.gov.br/sinapi.</t>
         </is>
@@ -5624,35 +5686,35 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="E21:I21"/>
     <mergeCell ref="E12:I12"/>
-    <mergeCell ref="E55:I55"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="E71:I71"/>
-    <mergeCell ref="E67:I67"/>
+    <mergeCell ref="E50:I50"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="E62:I62"/>
+    <mergeCell ref="E33:I33"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="E8:I8"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="E79:I79"/>
+    <mergeCell ref="E83:I83"/>
+    <mergeCell ref="E82:I82"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="E51:I51"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="E63:I63"/>
-    <mergeCell ref="E84:I84"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="E34:I34"/>
-    <mergeCell ref="E59:I59"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="E87:I87"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="E78:I78"/>
+    <mergeCell ref="E74:I74"/>
     <mergeCell ref="E6:I6"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="E80:I80"/>
+    <mergeCell ref="E49:I49"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="E70:I70"/>
     <mergeCell ref="E7:I7"/>
-    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="E54:I54"/>
+    <mergeCell ref="E32:I32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="E75:I75"/>
-    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E66:I66"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="E58:I58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
